--- a/Versão5/SUS/Ontologia_SomaSUS_4AU.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_4AU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B9B31A-8911-4A12-AAD3-250BA4935342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D57282-5DB4-46AA-9C37-31F2F76A86BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7883" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7883" uniqueCount="755">
   <si>
     <t>Key</t>
   </si>
@@ -2198,9 +2198,6 @@
   </si>
   <si>
     <t>Hospitalar Público</t>
-  </si>
-  <si>
-    <t>[ - ]</t>
   </si>
   <si>
     <t>It refers to an environment that is not totally cloistered.</t>
@@ -2966,7 +2963,163 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3533,15 +3686,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -3552,7 +3705,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -3563,7 +3716,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>49</v>
       </c>
@@ -3574,7 +3727,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
@@ -3585,7 +3738,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
@@ -3597,7 +3750,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
@@ -3609,7 +3762,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
@@ -3620,7 +3773,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>55</v>
       </c>
@@ -3631,7 +3784,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>56</v>
       </c>
@@ -3642,7 +3795,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -3653,7 +3806,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>60</v>
       </c>
@@ -3664,7 +3817,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
@@ -3675,7 +3828,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -3686,7 +3839,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>63</v>
       </c>
@@ -3697,7 +3850,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>64</v>
       </c>
@@ -3708,7 +3861,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>65</v>
       </c>
@@ -3719,7 +3872,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>66</v>
       </c>
@@ -3730,19 +3883,19 @@
         <v>626</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46258.575767824077</v>
+        <v>46264.57848113426</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>68</v>
       </c>
@@ -3753,7 +3906,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>69</v>
       </c>
@@ -3764,7 +3917,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>651</v>
       </c>
@@ -3775,7 +3928,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
         <v>630</v>
       </c>
@@ -3787,7 +3940,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
         <v>652</v>
       </c>
@@ -3799,7 +3952,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -3810,7 +3963,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="17" t="s">
         <v>71</v>
       </c>
@@ -3821,7 +3974,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="17" t="s">
         <v>624</v>
       </c>
@@ -3833,7 +3986,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="15" t="s">
         <v>662</v>
       </c>
@@ -3844,7 +3997,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="15" t="s">
         <v>664</v>
       </c>
@@ -3855,7 +4008,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="15" t="s">
         <v>666</v>
       </c>
@@ -3866,7 +4019,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>668</v>
       </c>
@@ -3877,7 +4030,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>670</v>
       </c>
@@ -3888,7 +4041,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>672</v>
       </c>
@@ -3899,7 +4052,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>674</v>
       </c>
@@ -3910,7 +4063,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>676</v>
       </c>
@@ -3921,7 +4074,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>678</v>
       </c>
@@ -3932,7 +4085,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>680</v>
       </c>
@@ -3943,7 +4096,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>682</v>
       </c>
@@ -3954,7 +4107,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="17" t="s">
         <v>684</v>
       </c>
@@ -3965,7 +4118,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="52" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="52" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>686</v>
       </c>
@@ -3976,7 +4129,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
         <v>688</v>
       </c>
@@ -4004,37 +4157,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.84375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.69140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.84375" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.15234375" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.3046875" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.3828125" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.3828125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.85546875" style="1"/>
+    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
@@ -4123,7 +4276,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -4208,19 +4361,19 @@
         <v>699</v>
       </c>
       <c r="Z2" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="69" t="s">
         <v>700</v>
       </c>
       <c r="AB2" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="49" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -4277,7 +4430,7 @@
         <v>433</v>
       </c>
       <c r="R3" s="48" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="S3" s="49" t="s">
         <v>1</v>
@@ -4305,19 +4458,19 @@
         <v>698</v>
       </c>
       <c r="Z3" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB3" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -4374,7 +4527,7 @@
         <v>434</v>
       </c>
       <c r="R4" s="48" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="S4" s="49" t="s">
         <v>1</v>
@@ -4402,19 +4555,19 @@
         <v>698</v>
       </c>
       <c r="Z4" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB4" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -4471,7 +4624,7 @@
         <v>435</v>
       </c>
       <c r="R5" s="48" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="S5" s="49" t="s">
         <v>1</v>
@@ -4499,19 +4652,19 @@
         <v>698</v>
       </c>
       <c r="Z5" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB5" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -4568,7 +4721,7 @@
         <v>596</v>
       </c>
       <c r="R6" s="48" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="S6" s="49" t="s">
         <v>1</v>
@@ -4596,19 +4749,19 @@
         <v>698</v>
       </c>
       <c r="Z6" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB6" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -4665,7 +4818,7 @@
         <v>436</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="S7" s="49" t="s">
         <v>1</v>
@@ -4693,19 +4846,19 @@
         <v>698</v>
       </c>
       <c r="Z7" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB7" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -4762,7 +4915,7 @@
         <v>437</v>
       </c>
       <c r="R8" s="48" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="S8" s="49" t="s">
         <v>1</v>
@@ -4790,19 +4943,19 @@
         <v>698</v>
       </c>
       <c r="Z8" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB8" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC8" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -4859,7 +5012,7 @@
         <v>597</v>
       </c>
       <c r="R9" s="48" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="S9" s="49" t="s">
         <v>1</v>
@@ -4887,19 +5040,19 @@
         <v>698</v>
       </c>
       <c r="Z9" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB9" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -4956,7 +5109,7 @@
         <v>438</v>
       </c>
       <c r="R10" s="48" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="S10" s="49" t="s">
         <v>1</v>
@@ -4984,19 +5137,19 @@
         <v>698</v>
       </c>
       <c r="Z10" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB10" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -5053,7 +5206,7 @@
         <v>439</v>
       </c>
       <c r="R11" s="48" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="S11" s="49" t="s">
         <v>1</v>
@@ -5081,19 +5234,19 @@
         <v>698</v>
       </c>
       <c r="Z11" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB11" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC11" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -5150,7 +5303,7 @@
         <v>604</v>
       </c>
       <c r="R12" s="48" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="S12" s="49" t="s">
         <v>1</v>
@@ -5178,19 +5331,19 @@
         <v>698</v>
       </c>
       <c r="Z12" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB12" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC12" s="49" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -5247,7 +5400,7 @@
         <v>602</v>
       </c>
       <c r="R13" s="48" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="S13" s="49" t="s">
         <v>1</v>
@@ -5275,19 +5428,19 @@
         <v>698</v>
       </c>
       <c r="Z13" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB13" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC13" s="49" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -5344,7 +5497,7 @@
         <v>603</v>
       </c>
       <c r="R14" s="48" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="S14" s="49" t="s">
         <v>1</v>
@@ -5372,19 +5525,19 @@
         <v>698</v>
       </c>
       <c r="Z14" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="48" t="s">
         <v>697</v>
       </c>
       <c r="AB14" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC14" s="49" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -5441,7 +5594,7 @@
         <v>615</v>
       </c>
       <c r="R15" s="48" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="S15" s="49" t="s">
         <v>1</v>
@@ -5469,19 +5622,19 @@
         <v>696</v>
       </c>
       <c r="Z15" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="48" t="s">
         <v>656</v>
       </c>
       <c r="AB15" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -5538,7 +5691,7 @@
         <v>617</v>
       </c>
       <c r="R16" s="48" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="S16" s="49" t="s">
         <v>1</v>
@@ -5566,19 +5719,19 @@
         <v>696</v>
       </c>
       <c r="Z16" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA16" s="48" t="s">
         <v>656</v>
       </c>
       <c r="AB16" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC16" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -5635,7 +5788,7 @@
         <v>618</v>
       </c>
       <c r="R17" s="48" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="S17" s="49" t="s">
         <v>1</v>
@@ -5663,19 +5816,19 @@
         <v>696</v>
       </c>
       <c r="Z17" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="48" t="s">
         <v>656</v>
       </c>
       <c r="AB17" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -5732,7 +5885,7 @@
         <v>619</v>
       </c>
       <c r="R18" s="48" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="S18" s="49" t="s">
         <v>1</v>
@@ -5760,19 +5913,19 @@
         <v>696</v>
       </c>
       <c r="Z18" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA18" s="48" t="s">
         <v>656</v>
       </c>
       <c r="AB18" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -5829,7 +5982,7 @@
         <v>440</v>
       </c>
       <c r="R19" s="48" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="S19" s="49" t="s">
         <v>1</v>
@@ -5857,19 +6010,19 @@
         <v>658</v>
       </c>
       <c r="Z19" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="48" t="s">
         <v>659</v>
       </c>
       <c r="AB19" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -5926,7 +6079,7 @@
         <v>440</v>
       </c>
       <c r="R20" s="48" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="S20" s="49" t="s">
         <v>1</v>
@@ -5954,19 +6107,19 @@
         <v>658</v>
       </c>
       <c r="Z20" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="48" t="s">
         <v>659</v>
       </c>
       <c r="AB20" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -6023,7 +6176,7 @@
         <v>609</v>
       </c>
       <c r="R21" s="48" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S21" s="49" t="s">
         <v>1</v>
@@ -6051,19 +6204,19 @@
         <v>658</v>
       </c>
       <c r="Z21" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="48" t="s">
         <v>659</v>
       </c>
       <c r="AB21" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC21" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -6120,7 +6273,7 @@
         <v>612</v>
       </c>
       <c r="R22" s="48" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="S22" s="49" t="s">
         <v>1</v>
@@ -6148,36 +6301,36 @@
         <v>658</v>
       </c>
       <c r="Z22" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="48" t="s">
         <v>659</v>
       </c>
       <c r="AB22" s="49" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="49" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46">
         <v>23</v>
       </c>
       <c r="B23" s="58" t="s">
+        <v>725</v>
+      </c>
+      <c r="C23" s="60" t="s">
         <v>726</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>727</v>
       </c>
       <c r="D23" s="60" t="s">
         <v>728</v>
       </c>
       <c r="E23" s="60" t="s">
+        <v>727</v>
+      </c>
+      <c r="F23" s="60" t="s">
         <v>729</v>
-      </c>
-      <c r="F23" s="60" t="s">
-        <v>730</v>
       </c>
       <c r="G23" s="79" t="s">
         <v>1</v>
@@ -6200,24 +6353,24 @@
       </c>
       <c r="M23" s="47" t="str">
         <f t="shared" si="6"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N23" s="47" t="str">
         <f t="shared" si="6"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O23" s="47" t="str">
         <f t="shared" si="6"/>
         <v>API Revit</v>
       </c>
       <c r="P23" s="48" t="s">
+        <v>730</v>
+      </c>
+      <c r="Q23" s="48" t="s">
         <v>731</v>
       </c>
-      <c r="Q23" s="48" t="s">
+      <c r="R23" s="48" t="s">
         <v>732</v>
-      </c>
-      <c r="R23" s="48" t="s">
-        <v>733</v>
       </c>
       <c r="S23" s="48" t="s">
         <v>1</v>
@@ -6228,11 +6381,11 @@
       </c>
       <c r="U23" s="48" t="str">
         <f t="shared" si="7"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V23" s="49" t="str">
         <f t="shared" si="7"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W23" s="48" t="s">
         <v>705</v>
@@ -6263,57 +6416,57 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:XFD1048576">
-    <cfRule type="cellIs" dxfId="26" priority="111" operator="equal">
+  <conditionalFormatting sqref="A24:X1048576 AD24:XFD1048576">
+    <cfRule type="cellIs" dxfId="43" priority="111" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="25" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:F1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:W20 T21:V22 W21:W23">
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z22 AB2:XFD22 Y3:Y22 AA3:AA22">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+  <conditionalFormatting sqref="AD2:XFD22">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6326,19 +6479,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
@@ -6403,7 +6556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -6471,7 +6624,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6487,14 +6640,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -6505,7 +6658,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -6518,7 +6671,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6530,42 +6683,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DD8556-259C-4223-B758-7C936DE6D1CE}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE242"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="31" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="31" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="31" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="31" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="31" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" style="31" customWidth="1"/>
-    <col min="10" max="10" width="5.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="32" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.15234375" style="31" customWidth="1"/>
+    <col min="3" max="3" width="11.3828125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="9.3828125" style="31" customWidth="1"/>
+    <col min="5" max="5" width="8.15234375" style="31" customWidth="1"/>
+    <col min="6" max="6" width="6.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.69140625" style="31" customWidth="1"/>
+    <col min="8" max="8" width="3.69140625" style="31" customWidth="1"/>
+    <col min="9" max="9" width="11.15234375" style="31" customWidth="1"/>
+    <col min="10" max="10" width="5.3046875" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3828125" style="32" customWidth="1"/>
+    <col min="13" max="13" width="11.3828125" style="31" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="44.140625" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" style="32" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="52.140625" style="31" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="32" customWidth="1"/>
+    <col min="15" max="15" width="44.15234375" customWidth="1"/>
+    <col min="16" max="16" width="8.3828125" style="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="52.15234375" style="31" customWidth="1"/>
+    <col min="18" max="18" width="5.15234375" style="32" customWidth="1"/>
     <col min="19" max="19" width="18" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" style="31" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" style="80" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.69140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.84375" style="31" customWidth="1"/>
+    <col min="22" max="22" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -6660,7 +6813,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -6755,7 +6908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22">
         <v>3</v>
       </c>
@@ -6850,7 +7003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22">
         <v>4</v>
       </c>
@@ -6945,7 +7098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="22">
         <v>5</v>
       </c>
@@ -7040,7 +7193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="22">
         <v>6</v>
       </c>
@@ -7135,7 +7288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="22">
         <v>7</v>
       </c>
@@ -7230,7 +7383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22">
         <v>8</v>
       </c>
@@ -7325,7 +7478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="22">
         <v>9</v>
       </c>
@@ -7420,7 +7573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22">
         <v>10</v>
       </c>
@@ -7515,7 +7668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22">
         <v>11</v>
       </c>
@@ -7610,7 +7763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22">
         <v>12</v>
       </c>
@@ -7705,7 +7858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="22">
         <v>13</v>
       </c>
@@ -7800,7 +7953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22">
         <v>14</v>
       </c>
@@ -7895,7 +8048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <v>15</v>
       </c>
@@ -7990,7 +8143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <v>16</v>
       </c>
@@ -8085,7 +8238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="22">
         <v>17</v>
       </c>
@@ -8180,7 +8333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22">
         <v>18</v>
       </c>
@@ -8275,7 +8428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22">
         <v>19</v>
       </c>
@@ -8370,7 +8523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22">
         <v>20</v>
       </c>
@@ -8465,7 +8618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22">
         <v>21</v>
       </c>
@@ -8560,7 +8713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22">
         <v>22</v>
       </c>
@@ -8655,7 +8808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22">
         <v>23</v>
       </c>
@@ -8750,7 +8903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="22">
         <v>24</v>
       </c>
@@ -8845,7 +8998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="22">
         <v>25</v>
       </c>
@@ -8940,7 +9093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="22">
         <v>26</v>
       </c>
@@ -9035,7 +9188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22">
         <v>27</v>
       </c>
@@ -9130,7 +9283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="22">
         <v>28</v>
       </c>
@@ -9225,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="22">
         <v>29</v>
       </c>
@@ -9320,7 +9473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22">
         <v>30</v>
       </c>
@@ -9415,7 +9568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="22">
         <v>31</v>
       </c>
@@ -9510,7 +9663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="22">
         <v>32</v>
       </c>
@@ -9605,7 +9758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="22">
         <v>33</v>
       </c>
@@ -9700,7 +9853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -9795,7 +9948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -9890,7 +10043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -9985,7 +10138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -10080,7 +10233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -10175,7 +10328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -10270,7 +10423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -10365,7 +10518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -10460,7 +10613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -10555,7 +10708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -10650,7 +10803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -10745,7 +10898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -10840,7 +10993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -10935,7 +11088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -11030,7 +11183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -11125,7 +11278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -11220,7 +11373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -11315,7 +11468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -11410,7 +11563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -11505,7 +11658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -11600,7 +11753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -11695,7 +11848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -11790,7 +11943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -11885,7 +12038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -11980,7 +12133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -12075,7 +12228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -12170,7 +12323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -12265,7 +12418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -12360,7 +12513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -12455,7 +12608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -12550,7 +12703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -12645,7 +12798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -12740,7 +12893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -12835,7 +12988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -12930,7 +13083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -13025,7 +13178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -13120,7 +13273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -13215,7 +13368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -13310,7 +13463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -13405,7 +13558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -13500,7 +13653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -13595,7 +13748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -13690,7 +13843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -13785,7 +13938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -13880,7 +14033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -13975,7 +14128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -14070,7 +14223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -14165,7 +14318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -14260,7 +14413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -14355,7 +14508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -14450,7 +14603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -14545,7 +14698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -14640,7 +14793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -14735,7 +14888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -14830,7 +14983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -14925,7 +15078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -15020,7 +15173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -15115,7 +15268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -15210,7 +15363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -15305,7 +15458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -15400,7 +15553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -15495,7 +15648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -15590,7 +15743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -15685,7 +15838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -15780,7 +15933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -15875,7 +16028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -15970,7 +16123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -16065,7 +16218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -16160,7 +16313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -16255,7 +16408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -16350,7 +16503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -16445,7 +16598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -16540,7 +16693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -16635,7 +16788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -16730,7 +16883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -16825,7 +16978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -16920,7 +17073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -17015,7 +17168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -17110,7 +17263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -17205,7 +17358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -17300,7 +17453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -17395,7 +17548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -17490,7 +17643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -17585,7 +17738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -17680,7 +17833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -17775,7 +17928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -17870,7 +18023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -17965,7 +18118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -18060,7 +18213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -18155,7 +18308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -18250,7 +18403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -18345,7 +18498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -18440,7 +18593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -18535,7 +18688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -18630,7 +18783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -18725,7 +18878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -18820,7 +18973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -18915,7 +19068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="22">
         <v>131</v>
       </c>
@@ -19010,7 +19163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -19105,7 +19258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -19200,7 +19353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -19295,7 +19448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -19390,7 +19543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -19485,7 +19638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -19580,7 +19733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -19675,7 +19828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -19770,7 +19923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -19865,7 +20018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -19960,7 +20113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -20055,7 +20208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -20150,7 +20303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="22">
         <v>144</v>
       </c>
@@ -20245,7 +20398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="22">
         <v>145</v>
       </c>
@@ -20340,7 +20493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="22">
         <v>146</v>
       </c>
@@ -20435,7 +20588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="22">
         <v>147</v>
       </c>
@@ -20530,7 +20683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="22">
         <v>148</v>
       </c>
@@ -20625,7 +20778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="22">
         <v>149</v>
       </c>
@@ -20720,7 +20873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="22">
         <v>150</v>
       </c>
@@ -20815,7 +20968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="22">
         <v>151</v>
       </c>
@@ -20910,7 +21063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="22">
         <v>152</v>
       </c>
@@ -21005,7 +21158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="22">
         <v>153</v>
       </c>
@@ -21100,7 +21253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="22">
         <v>154</v>
       </c>
@@ -21195,7 +21348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="22">
         <v>155</v>
       </c>
@@ -21290,7 +21443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="22">
         <v>156</v>
       </c>
@@ -21385,7 +21538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="22">
         <v>157</v>
       </c>
@@ -21480,7 +21633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="22">
         <v>158</v>
       </c>
@@ -21575,7 +21728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="22">
         <v>159</v>
       </c>
@@ -21670,7 +21823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="22">
         <v>160</v>
       </c>
@@ -21765,7 +21918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="22">
         <v>161</v>
       </c>
@@ -21860,7 +22013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="22">
         <v>162</v>
       </c>
@@ -21955,7 +22108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="22">
         <v>163</v>
       </c>
@@ -22050,7 +22203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="22">
         <v>164</v>
       </c>
@@ -22145,7 +22298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="22">
         <v>165</v>
       </c>
@@ -22240,7 +22393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="22">
         <v>166</v>
       </c>
@@ -22335,7 +22488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="22">
         <v>167</v>
       </c>
@@ -22430,7 +22583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="22">
         <v>168</v>
       </c>
@@ -22525,7 +22678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="22">
         <v>169</v>
       </c>
@@ -22620,7 +22773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="22">
         <v>170</v>
       </c>
@@ -22715,7 +22868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="22">
         <v>171</v>
       </c>
@@ -22810,7 +22963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="22">
         <v>172</v>
       </c>
@@ -22905,7 +23058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="22">
         <v>173</v>
       </c>
@@ -23000,7 +23153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="22">
         <v>174</v>
       </c>
@@ -23095,7 +23248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="22">
         <v>175</v>
       </c>
@@ -23190,7 +23343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="22">
         <v>176</v>
       </c>
@@ -23285,7 +23438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="22">
         <v>177</v>
       </c>
@@ -23380,7 +23533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="22">
         <v>178</v>
       </c>
@@ -23475,7 +23628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="22">
         <v>179</v>
       </c>
@@ -23570,7 +23723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="22">
         <v>180</v>
       </c>
@@ -23665,7 +23818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="22">
         <v>181</v>
       </c>
@@ -23760,7 +23913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="22">
         <v>182</v>
       </c>
@@ -23855,7 +24008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="22">
         <v>183</v>
       </c>
@@ -23950,7 +24103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="22">
         <v>184</v>
       </c>
@@ -24045,7 +24198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="22">
         <v>185</v>
       </c>
@@ -24140,7 +24293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="22">
         <v>186</v>
       </c>
@@ -24235,7 +24388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="22">
         <v>187</v>
       </c>
@@ -24330,7 +24483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="22">
         <v>188</v>
       </c>
@@ -24425,7 +24578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="22">
         <v>189</v>
       </c>
@@ -24520,7 +24673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="22">
         <v>190</v>
       </c>
@@ -24615,7 +24768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="22">
         <v>191</v>
       </c>
@@ -24710,7 +24863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="22">
         <v>192</v>
       </c>
@@ -24805,7 +24958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="22">
         <v>193</v>
       </c>
@@ -24900,7 +25053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="22">
         <v>194</v>
       </c>
@@ -24995,7 +25148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="22">
         <v>195</v>
       </c>
@@ -25090,7 +25243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="22">
         <v>196</v>
       </c>
@@ -25185,7 +25338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="22">
         <v>197</v>
       </c>
@@ -25280,7 +25433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="22">
         <v>198</v>
       </c>
@@ -25375,7 +25528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="22">
         <v>199</v>
       </c>
@@ -25470,7 +25623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="22">
         <v>200</v>
       </c>
@@ -25565,7 +25718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="22">
         <v>201</v>
       </c>
@@ -25660,7 +25813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="22">
         <v>202</v>
       </c>
@@ -25755,7 +25908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="22">
         <v>203</v>
       </c>
@@ -25850,7 +26003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="22">
         <v>204</v>
       </c>
@@ -25945,7 +26098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="22">
         <v>205</v>
       </c>
@@ -26040,7 +26193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="22">
         <v>206</v>
       </c>
@@ -26135,7 +26288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="22">
         <v>207</v>
       </c>
@@ -26230,7 +26383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="22">
         <v>208</v>
       </c>
@@ -26325,7 +26478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="22">
         <v>209</v>
       </c>
@@ -26420,7 +26573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="22">
         <v>210</v>
       </c>
@@ -26515,7 +26668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="22">
         <v>211</v>
       </c>
@@ -26610,7 +26763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="22">
         <v>212</v>
       </c>
@@ -26705,7 +26858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="22">
         <v>213</v>
       </c>
@@ -26800,7 +26953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="22">
         <v>214</v>
       </c>
@@ -26895,7 +27048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="22">
         <v>215</v>
       </c>
@@ -26990,7 +27143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="22">
         <v>216</v>
       </c>
@@ -27085,7 +27238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="22">
         <v>217</v>
       </c>
@@ -27180,7 +27333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="22">
         <v>218</v>
       </c>
@@ -27275,7 +27428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="22">
         <v>219</v>
       </c>
@@ -27370,7 +27523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="22">
         <v>220</v>
       </c>
@@ -27465,7 +27618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="22">
         <v>221</v>
       </c>
@@ -27560,7 +27713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="22">
         <v>222</v>
       </c>
@@ -27655,7 +27808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="22">
         <v>223</v>
       </c>
@@ -27750,7 +27903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="22">
         <v>224</v>
       </c>
@@ -27845,7 +27998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="22">
         <v>225</v>
       </c>
@@ -27940,7 +28093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="22">
         <v>226</v>
       </c>
@@ -28035,7 +28188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="22">
         <v>227</v>
       </c>
@@ -28130,7 +28283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="22">
         <v>228</v>
       </c>
@@ -28225,7 +28378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="22">
         <v>229</v>
       </c>
@@ -28320,7 +28473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="22">
         <v>230</v>
       </c>
@@ -28415,7 +28568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="22">
         <v>231</v>
       </c>
@@ -28510,7 +28663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="22">
         <v>232</v>
       </c>
@@ -28605,7 +28758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="22">
         <v>233</v>
       </c>
@@ -28700,7 +28853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="22">
         <v>234</v>
       </c>
@@ -28795,7 +28948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="22">
         <v>235</v>
       </c>
@@ -28890,7 +29043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="22">
         <v>236</v>
       </c>
@@ -28985,7 +29138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="22">
         <v>237</v>
       </c>
@@ -29080,15 +29233,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="22">
         <v>238</v>
       </c>
       <c r="B238" s="81" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C238" s="88" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D238" s="37" t="s">
         <v>1</v>
@@ -29106,13 +29259,13 @@
         <v>385</v>
       </c>
       <c r="I238" s="83" t="s">
+        <v>734</v>
+      </c>
+      <c r="J238" s="82" t="s">
         <v>735</v>
       </c>
-      <c r="J238" s="82" t="s">
+      <c r="K238" s="83" t="s">
         <v>736</v>
-      </c>
-      <c r="K238" s="83" t="s">
-        <v>737</v>
       </c>
       <c r="L238" s="30" t="s">
         <v>1</v>
@@ -29124,14 +29277,14 @@
         <v>386</v>
       </c>
       <c r="O238" s="83" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P238" s="85" t="str">
         <f t="shared" ref="P238:P242" si="0">IF(Q238="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q238" s="86" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="R238" s="84" t="s">
         <v>1</v>
@@ -29176,15 +29329,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="22">
         <v>239</v>
       </c>
       <c r="B239" s="81" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C239" s="88" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D239" s="37" t="s">
         <v>1</v>
@@ -29202,13 +29355,13 @@
         <v>385</v>
       </c>
       <c r="I239" s="83" t="s">
+        <v>734</v>
+      </c>
+      <c r="J239" s="82" t="s">
         <v>735</v>
       </c>
-      <c r="J239" s="82" t="s">
-        <v>736</v>
-      </c>
       <c r="K239" s="83" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L239" s="30" t="s">
         <v>1</v>
@@ -29220,14 +29373,14 @@
         <v>386</v>
       </c>
       <c r="O239" s="83" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P239" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q239" s="86" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="R239" s="84" t="s">
         <v>1</v>
@@ -29272,15 +29425,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="22">
         <v>240</v>
       </c>
       <c r="B240" s="81" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C240" s="88" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D240" s="37" t="s">
         <v>1</v>
@@ -29298,13 +29451,13 @@
         <v>385</v>
       </c>
       <c r="I240" s="83" t="s">
+        <v>734</v>
+      </c>
+      <c r="J240" s="82" t="s">
         <v>735</v>
       </c>
-      <c r="J240" s="82" t="s">
-        <v>736</v>
-      </c>
       <c r="K240" s="83" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L240" s="30" t="s">
         <v>1</v>
@@ -29316,14 +29469,14 @@
         <v>386</v>
       </c>
       <c r="O240" s="83" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="P240" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q240" s="86" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="R240" s="84" t="s">
         <v>1</v>
@@ -29368,15 +29521,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="22">
         <v>241</v>
       </c>
       <c r="B241" s="81" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C241" s="88" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D241" s="37" t="s">
         <v>1</v>
@@ -29394,13 +29547,13 @@
         <v>385</v>
       </c>
       <c r="I241" s="83" t="s">
+        <v>734</v>
+      </c>
+      <c r="J241" s="82" t="s">
         <v>735</v>
       </c>
-      <c r="J241" s="82" t="s">
-        <v>736</v>
-      </c>
       <c r="K241" s="83" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="L241" s="30" t="s">
         <v>1</v>
@@ -29412,14 +29565,14 @@
         <v>386</v>
       </c>
       <c r="O241" s="83" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="P241" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q241" s="86" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R241" s="84" t="s">
         <v>1</v>
@@ -29464,15 +29617,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="89">
         <v>242</v>
       </c>
       <c r="B242" s="81" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C242" s="88" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D242" s="37" t="s">
         <v>1</v>
@@ -29490,13 +29643,13 @@
         <v>385</v>
       </c>
       <c r="I242" s="83" t="s">
+        <v>734</v>
+      </c>
+      <c r="J242" s="82" t="s">
         <v>735</v>
       </c>
-      <c r="J242" s="82" t="s">
-        <v>736</v>
-      </c>
       <c r="K242" s="83" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="L242" s="30" t="s">
         <v>1</v>
@@ -29508,14 +29661,14 @@
         <v>386</v>
       </c>
       <c r="O242" s="83" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="P242" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q242" s="86" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="R242" s="84" t="s">
         <v>1</v>
@@ -29562,41 +29715,41 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B238:B242">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R238:U242">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:AE1">
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SUS/Ontologia_SomaSUS_4AU.xlsx
+++ b/Versão5/SUS/Ontologia_SomaSUS_4AU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D57282-5DB4-46AA-9C37-31F2F76A86BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88081720-1F12-477A-BC9E-6E7ADBFB5BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7883" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7990" uniqueCount="773">
   <si>
     <t>Key</t>
   </si>
@@ -2269,18 +2269,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2345,6 +2333,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2449,7 +2503,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2584,18 +2638,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFDE75"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFDE75"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2646,6 +2688,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -2701,7 +2749,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2864,31 +2912,7 @@
     <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2900,25 +2924,25 @@
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2931,7 +2955,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2940,186 +2964,45 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <b val="0"/>
@@ -3235,6 +3118,24 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3686,15 +3587,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -3705,7 +3606,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -3716,7 +3617,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>49</v>
       </c>
@@ -3727,7 +3628,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
@@ -3738,7 +3639,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
@@ -3750,7 +3651,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
@@ -3762,7 +3663,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
@@ -3773,7 +3674,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>55</v>
       </c>
@@ -3784,7 +3685,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>56</v>
       </c>
@@ -3795,7 +3696,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -3806,7 +3707,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>60</v>
       </c>
@@ -3817,7 +3718,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
@@ -3828,7 +3729,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -3839,7 +3740,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>63</v>
       </c>
@@ -3850,7 +3751,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>64</v>
       </c>
@@ -3861,7 +3762,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>65</v>
       </c>
@@ -3872,7 +3773,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>66</v>
       </c>
@@ -3883,19 +3784,19 @@
         <v>626</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46264.57848113426</v>
+        <v>46268.701054166668</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>68</v>
       </c>
@@ -3906,7 +3807,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>69</v>
       </c>
@@ -3917,7 +3818,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>651</v>
       </c>
@@ -3928,7 +3829,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>630</v>
       </c>
@@ -3940,7 +3841,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>652</v>
       </c>
@@ -3952,7 +3853,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -3963,7 +3864,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>71</v>
       </c>
@@ -3974,7 +3875,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>624</v>
       </c>
@@ -3986,7 +3887,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>662</v>
       </c>
@@ -3997,7 +3898,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>664</v>
       </c>
@@ -4008,7 +3909,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>666</v>
       </c>
@@ -4019,7 +3920,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="15" t="s">
         <v>668</v>
       </c>
@@ -4030,7 +3931,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="15" t="s">
         <v>670</v>
       </c>
@@ -4041,7 +3942,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>672</v>
       </c>
@@ -4052,7 +3953,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="15" t="s">
         <v>674</v>
       </c>
@@ -4063,7 +3964,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="15" t="s">
         <v>676</v>
       </c>
@@ -4074,7 +3975,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="15" t="s">
         <v>678</v>
       </c>
@@ -4085,7 +3986,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="15" t="s">
         <v>680</v>
       </c>
@@ -4096,7 +3997,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="50" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="15" t="s">
         <v>682</v>
       </c>
@@ -4107,7 +4008,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>684</v>
       </c>
@@ -4118,7 +4019,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="52" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="52" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="15" t="s">
         <v>686</v>
       </c>
@@ -4129,7 +4030,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
         <v>688</v>
       </c>
@@ -4156,38 +4057,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD27"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.69140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.69140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.3046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.3828125" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.84375" style="1"/>
+    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" s="3" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
@@ -4206,19 +4107,19 @@
       <c r="F1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="78" t="s">
+      <c r="I1" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="78" t="s">
+      <c r="J1" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="78" t="s">
+      <c r="K1" s="70" t="s">
         <v>34</v>
       </c>
       <c r="L1" s="26" t="s">
@@ -4239,10 +4140,10 @@
       <c r="Q1" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="74" t="s">
+      <c r="R1" s="66" t="s">
         <v>622</v>
       </c>
-      <c r="S1" s="67" t="s">
+      <c r="S1" s="59" t="s">
         <v>384</v>
       </c>
       <c r="T1" s="26" t="s">
@@ -4257,7 +4158,7 @@
       <c r="W1" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="75" t="s">
+      <c r="X1" s="67" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="26" t="s">
@@ -4275,39 +4176,42 @@
       <c r="AC1" s="26" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD1" s="26" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="46">
         <v>2</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="80" t="s">
         <v>547</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="80" t="s">
         <v>695</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="84" t="s">
         <v>408</v>
       </c>
-      <c r="G2" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="79" t="s">
+      <c r="G2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="47" t="str">
@@ -4353,17 +4257,17 @@
       <c r="W2" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X2" s="62" t="str">
-        <f t="shared" ref="X2:X23" si="3">CONCATENATE("Key-SUS-",A2)</f>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X27" si="3">CONCATENATE("Key-SUS-",A2)</f>
         <v>Key-SUS-2</v>
       </c>
-      <c r="Y2" s="68" t="s">
+      <c r="Y2" s="60" t="s">
         <v>699</v>
       </c>
       <c r="Z2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="69" t="s">
+      <c r="AA2" s="61" t="s">
         <v>700</v>
       </c>
       <c r="AB2" s="49" t="s">
@@ -4372,39 +4276,42 @@
       <c r="AC2" s="49" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD2" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46">
         <v>3</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="E3" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F3" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="G3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="79" t="s">
+      <c r="G3" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="47" t="str">
@@ -4450,7 +4357,7 @@
       <c r="W3" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X3" s="62" t="str">
+      <c r="X3" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-3</v>
       </c>
@@ -4469,39 +4376,42 @@
       <c r="AC3" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD3" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="46">
         <v>4</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F4" s="64" t="s">
         <v>413</v>
       </c>
-      <c r="G4" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="79" t="s">
+      <c r="G4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L4" s="47" t="str">
@@ -4547,7 +4457,7 @@
       <c r="W4" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X4" s="62" t="str">
+      <c r="X4" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-4</v>
       </c>
@@ -4566,39 +4476,42 @@
       <c r="AC4" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD4" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46">
         <v>5</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F5" s="64" t="s">
         <v>415</v>
       </c>
-      <c r="G5" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="79" t="s">
+      <c r="G5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L5" s="47" t="str">
@@ -4644,7 +4557,7 @@
       <c r="W5" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X5" s="62" t="str">
+      <c r="X5" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-5</v>
       </c>
@@ -4663,39 +4576,42 @@
       <c r="AC5" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD5" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46">
         <v>6</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F6" s="64" t="s">
         <v>418</v>
       </c>
-      <c r="G6" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="79" t="s">
+      <c r="G6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L6" s="47" t="str">
@@ -4741,7 +4657,7 @@
       <c r="W6" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X6" s="62" t="str">
+      <c r="X6" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-6</v>
       </c>
@@ -4760,39 +4676,42 @@
       <c r="AC6" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD6" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46">
         <v>7</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="63" t="s">
+      <c r="E7" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F7" s="64" t="s">
         <v>416</v>
       </c>
-      <c r="G7" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="79" t="s">
+      <c r="G7" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="47" t="str">
@@ -4838,7 +4757,7 @@
       <c r="W7" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X7" s="62" t="str">
+      <c r="X7" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-7</v>
       </c>
@@ -4857,39 +4776,42 @@
       <c r="AC7" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD7" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="46">
         <v>8</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E8" s="63" t="s">
+      <c r="E8" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F8" s="64" t="s">
         <v>420</v>
       </c>
-      <c r="G8" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="79" t="s">
+      <c r="G8" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="47" t="str">
@@ -4935,7 +4857,7 @@
       <c r="W8" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X8" s="62" t="str">
+      <c r="X8" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-8</v>
       </c>
@@ -4954,39 +4876,42 @@
       <c r="AC8" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD8" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46">
         <v>9</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F9" s="64" t="s">
         <v>414</v>
       </c>
-      <c r="G9" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="79" t="s">
+      <c r="G9" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="47" t="str">
@@ -5032,7 +4957,7 @@
       <c r="W9" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X9" s="62" t="str">
+      <c r="X9" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-9</v>
       </c>
@@ -5051,39 +4976,42 @@
       <c r="AC9" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD9" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="46">
         <v>10</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F10" s="64" t="s">
         <v>417</v>
       </c>
-      <c r="G10" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="79" t="s">
+      <c r="G10" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="47" t="str">
@@ -5129,7 +5057,7 @@
       <c r="W10" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X10" s="62" t="str">
+      <c r="X10" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-10</v>
       </c>
@@ -5148,39 +5076,42 @@
       <c r="AC10" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD10" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46">
         <v>11</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="85" t="s">
         <v>548</v>
       </c>
       <c r="F11" s="65" t="s">
         <v>419</v>
       </c>
-      <c r="G11" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="79" t="s">
+      <c r="G11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L11" s="47" t="str">
@@ -5226,7 +5157,7 @@
       <c r="W11" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X11" s="62" t="str">
+      <c r="X11" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-11</v>
       </c>
@@ -5245,39 +5176,42 @@
       <c r="AC11" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD11" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="46">
         <v>12</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="85" t="s">
         <v>549</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="86" t="s">
         <v>402</v>
       </c>
-      <c r="G12" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="79" t="s">
+      <c r="G12" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="47" t="str">
@@ -5323,7 +5257,7 @@
       <c r="W12" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X12" s="62" t="str">
+      <c r="X12" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-12</v>
       </c>
@@ -5342,39 +5276,42 @@
       <c r="AC12" s="49" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD12" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="46">
         <v>13</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="85" t="s">
         <v>549</v>
       </c>
-      <c r="F13" s="66" t="s">
+      <c r="F13" s="86" t="s">
         <v>400</v>
       </c>
-      <c r="G13" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="79" t="s">
+      <c r="G13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L13" s="47" t="str">
@@ -5420,7 +5357,7 @@
       <c r="W13" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X13" s="62" t="str">
+      <c r="X13" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-13</v>
       </c>
@@ -5439,39 +5376,42 @@
       <c r="AC13" s="49" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD13" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="46">
         <v>14</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="85" t="s">
         <v>546</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="85" t="s">
         <v>549</v>
       </c>
-      <c r="F14" s="66" t="s">
+      <c r="F14" s="86" t="s">
         <v>401</v>
       </c>
-      <c r="G14" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="79" t="s">
+      <c r="G14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L14" s="47" t="str">
@@ -5517,7 +5457,7 @@
       <c r="W14" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X14" s="62" t="str">
+      <c r="X14" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-14</v>
       </c>
@@ -5536,39 +5476,42 @@
       <c r="AC14" s="49" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD14" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46">
         <v>15</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="85" t="s">
         <v>550</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="86" t="s">
         <v>613</v>
       </c>
-      <c r="G15" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="79" t="s">
+      <c r="G15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="47" t="str">
@@ -5614,7 +5557,7 @@
       <c r="W15" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X15" s="62" t="str">
+      <c r="X15" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-15</v>
       </c>
@@ -5633,39 +5576,42 @@
       <c r="AC15" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD15" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="46">
         <v>16</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="85" t="s">
         <v>550</v>
       </c>
-      <c r="F16" s="66" t="s">
+      <c r="F16" s="86" t="s">
         <v>403</v>
       </c>
-      <c r="G16" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="79" t="s">
+      <c r="G16" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L16" s="47" t="str">
@@ -5711,7 +5657,7 @@
       <c r="W16" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X16" s="62" t="str">
+      <c r="X16" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-16</v>
       </c>
@@ -5730,39 +5676,42 @@
       <c r="AC16" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD16" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="46">
         <v>17</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="85" t="s">
         <v>550</v>
       </c>
-      <c r="F17" s="66" t="s">
+      <c r="F17" s="86" t="s">
         <v>404</v>
       </c>
-      <c r="G17" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="79" t="s">
+      <c r="G17" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L17" s="47" t="str">
@@ -5808,7 +5757,7 @@
       <c r="W17" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X17" s="62" t="str">
+      <c r="X17" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-17</v>
       </c>
@@ -5827,39 +5776,42 @@
       <c r="AC17" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD17" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="46">
         <v>18</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="63" t="s">
+      <c r="D18" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="85" t="s">
         <v>550</v>
       </c>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="86" t="s">
         <v>605</v>
       </c>
-      <c r="G18" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="79" t="s">
+      <c r="G18" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L18" s="47" t="str">
@@ -5905,7 +5857,7 @@
       <c r="W18" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X18" s="62" t="str">
+      <c r="X18" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-18</v>
       </c>
@@ -5924,39 +5876,42 @@
       <c r="AC18" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="46">
         <v>19</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="85" t="s">
         <v>550</v>
       </c>
-      <c r="F19" s="66" t="s">
+      <c r="F19" s="86" t="s">
         <v>607</v>
       </c>
-      <c r="G19" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="79" t="s">
+      <c r="G19" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L19" s="47" t="str">
@@ -6002,7 +5957,7 @@
       <c r="W19" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X19" s="62" t="str">
+      <c r="X19" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-19</v>
       </c>
@@ -6021,39 +5976,42 @@
       <c r="AC19" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="46">
         <v>20</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="85" t="s">
         <v>620</v>
       </c>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="86" t="s">
         <v>405</v>
       </c>
-      <c r="G20" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="79" t="s">
+      <c r="G20" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L20" s="47" t="str">
@@ -6099,7 +6057,7 @@
       <c r="W20" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X20" s="62" t="str">
+      <c r="X20" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-20</v>
       </c>
@@ -6118,39 +6076,42 @@
       <c r="AC20" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD20" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="46">
         <v>21</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E21" s="63" t="s">
+      <c r="E21" s="85" t="s">
         <v>620</v>
       </c>
-      <c r="F21" s="66" t="s">
+      <c r="F21" s="86" t="s">
         <v>621</v>
       </c>
-      <c r="G21" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="79" t="s">
+      <c r="G21" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L21" s="47" t="str">
@@ -6196,7 +6157,7 @@
       <c r="W21" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X21" s="62" t="str">
+      <c r="X21" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-21</v>
       </c>
@@ -6215,39 +6176,42 @@
       <c r="AC21" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD21" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="46">
         <v>22</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="83" t="s">
         <v>694</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="85" t="s">
         <v>595</v>
       </c>
-      <c r="E22" s="63" t="s">
+      <c r="E22" s="85" t="s">
         <v>620</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="86" t="s">
         <v>610</v>
       </c>
-      <c r="G22" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="79" t="s">
+      <c r="G22" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="71" t="s">
         <v>1</v>
       </c>
       <c r="L22" s="47" t="str">
@@ -6293,7 +6257,7 @@
       <c r="W22" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X22" s="62" t="str">
+      <c r="X22" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-22</v>
       </c>
@@ -6312,43 +6276,46 @@
       <c r="AC22" s="49" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" s="77" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD22" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="46">
         <v>23</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="83" t="s">
         <v>725</v>
       </c>
-      <c r="C23" s="60" t="s">
+      <c r="C23" s="80" t="s">
         <v>726</v>
       </c>
-      <c r="D23" s="60" t="s">
+      <c r="D23" s="80" t="s">
         <v>728</v>
       </c>
-      <c r="E23" s="60" t="s">
+      <c r="E23" s="80" t="s">
         <v>727</v>
       </c>
-      <c r="F23" s="60" t="s">
-        <v>729</v>
-      </c>
-      <c r="G23" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="79" t="s">
+      <c r="F23" s="80" t="s">
+        <v>751</v>
+      </c>
+      <c r="G23" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="82" t="s">
         <v>1</v>
       </c>
       <c r="L23" s="47" t="str">
-        <f t="shared" ref="L23:O23" si="6">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
+        <f t="shared" ref="L23:O27" si="6">SUBSTITUTE(CONCATENATE("", C23), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M23" s="47" t="str">
@@ -6361,22 +6328,22 @@
       </c>
       <c r="O23" s="47" t="str">
         <f t="shared" si="6"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P23" s="48" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="Q23" s="48" t="s">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="R23" s="48" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
       <c r="S23" s="48" t="s">
         <v>1</v>
       </c>
       <c r="T23" s="48" t="str">
-        <f t="shared" ref="T23:V23" si="7">SUBSTITUTE(C23, ".", " ")</f>
+        <f t="shared" ref="T23:V27" si="7">SUBSTITUTE(C23, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U23" s="48" t="str">
@@ -6390,23 +6357,426 @@
       <c r="W23" s="48" t="s">
         <v>705</v>
       </c>
-      <c r="X23" s="62" t="str">
+      <c r="X23" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-SUS-23</v>
       </c>
-      <c r="Y23" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="76" t="s">
+      <c r="Y23" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="46">
+        <v>24</v>
+      </c>
+      <c r="B24" s="83" t="s">
+        <v>725</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>726</v>
+      </c>
+      <c r="D24" s="80" t="s">
+        <v>728</v>
+      </c>
+      <c r="E24" s="80" t="s">
+        <v>727</v>
+      </c>
+      <c r="F24" s="80" t="s">
+        <v>755</v>
+      </c>
+      <c r="G24" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>De API</v>
+      </c>
+      <c r="M24" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Macros</v>
+      </c>
+      <c r="N24" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O24" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P24" s="48" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q24" s="48" t="s">
+        <v>757</v>
+      </c>
+      <c r="R24" s="48" t="s">
+        <v>758</v>
+      </c>
+      <c r="S24" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>De API</v>
+      </c>
+      <c r="U24" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>Macros</v>
+      </c>
+      <c r="V24" s="49" t="str">
+        <f t="shared" si="7"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W24" s="48" t="s">
+        <v>705</v>
+      </c>
+      <c r="X24" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-24</v>
+      </c>
+      <c r="Y24" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="46">
+        <v>25</v>
+      </c>
+      <c r="B25" s="83" t="s">
+        <v>725</v>
+      </c>
+      <c r="C25" s="80" t="s">
+        <v>726</v>
+      </c>
+      <c r="D25" s="80" t="s">
+        <v>728</v>
+      </c>
+      <c r="E25" s="80" t="s">
+        <v>727</v>
+      </c>
+      <c r="F25" s="80" t="s">
+        <v>759</v>
+      </c>
+      <c r="G25" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>De API</v>
+      </c>
+      <c r="M25" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Macros</v>
+      </c>
+      <c r="N25" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O25" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P25" s="48" t="s">
+        <v>760</v>
+      </c>
+      <c r="Q25" s="48" t="s">
+        <v>761</v>
+      </c>
+      <c r="R25" s="48" t="s">
+        <v>762</v>
+      </c>
+      <c r="S25" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>De API</v>
+      </c>
+      <c r="U25" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>Macros</v>
+      </c>
+      <c r="V25" s="49" t="str">
+        <f t="shared" si="7"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W25" s="48" t="s">
+        <v>705</v>
+      </c>
+      <c r="X25" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-25</v>
+      </c>
+      <c r="Y25" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="46">
+        <v>26</v>
+      </c>
+      <c r="B26" s="83" t="s">
+        <v>725</v>
+      </c>
+      <c r="C26" s="80" t="s">
+        <v>726</v>
+      </c>
+      <c r="D26" s="80" t="s">
+        <v>728</v>
+      </c>
+      <c r="E26" s="80" t="s">
+        <v>727</v>
+      </c>
+      <c r="F26" s="80" t="s">
+        <v>763</v>
+      </c>
+      <c r="G26" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>De API</v>
+      </c>
+      <c r="M26" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Macros</v>
+      </c>
+      <c r="N26" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O26" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>764</v>
+      </c>
+      <c r="Q26" s="48" t="s">
+        <v>765</v>
+      </c>
+      <c r="R26" s="48" t="s">
+        <v>766</v>
+      </c>
+      <c r="S26" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="T26" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>De API</v>
+      </c>
+      <c r="U26" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>Macros</v>
+      </c>
+      <c r="V26" s="49" t="str">
+        <f t="shared" si="7"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W26" s="48" t="s">
+        <v>705</v>
+      </c>
+      <c r="X26" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-26</v>
+      </c>
+      <c r="Y26" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="46">
+        <v>27</v>
+      </c>
+      <c r="B27" s="83" t="s">
+        <v>725</v>
+      </c>
+      <c r="C27" s="80" t="s">
+        <v>726</v>
+      </c>
+      <c r="D27" s="80" t="s">
+        <v>728</v>
+      </c>
+      <c r="E27" s="80" t="s">
+        <v>767</v>
+      </c>
+      <c r="F27" s="80" t="s">
+        <v>768</v>
+      </c>
+      <c r="G27" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>De API</v>
+      </c>
+      <c r="M27" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Macros</v>
+      </c>
+      <c r="N27" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O27" s="47" t="str">
+        <f t="shared" si="6"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P27" s="48" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q27" s="48" t="s">
+        <v>770</v>
+      </c>
+      <c r="R27" s="48" t="s">
+        <v>771</v>
+      </c>
+      <c r="S27" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>De API</v>
+      </c>
+      <c r="U27" s="48" t="str">
+        <f t="shared" si="7"/>
+        <v>Macros</v>
+      </c>
+      <c r="V27" s="49" t="str">
+        <f t="shared" si="7"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W27" s="48" t="s">
+        <v>705</v>
+      </c>
+      <c r="X27" s="58" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-SUS-27</v>
+      </c>
+      <c r="Y27" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="48" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6415,58 +6785,66 @@
     <sortCondition ref="A1:A18"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:X1048576 AD24:XFD1048576">
-    <cfRule type="cellIs" dxfId="43" priority="111" operator="equal">
+  <conditionalFormatting sqref="A28:X1048576 AD28:XFD1048576">
+    <cfRule type="cellIs" dxfId="28" priority="119" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F2 L2:Q22">
-    <cfRule type="cellIs" dxfId="42" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F22">
-    <cfRule type="cellIs" dxfId="41" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E27:F27">
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="40" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="39" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F22">
-    <cfRule type="duplicateValues" dxfId="38" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+  <conditionalFormatting sqref="F23:F26">
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="112"/>
+  <conditionalFormatting sqref="F28:F1048576">
+    <cfRule type="duplicateValues" dxfId="15" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R22">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:W20 T21:V22 W21:W23">
-    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
+  <conditionalFormatting sqref="T2:W22">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD22">
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
+  <conditionalFormatting sqref="W23:W27">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:XFD22">
+    <cfRule type="cellIs" dxfId="11" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6479,19 +6857,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.3828125" style="5"/>
+    <col min="22" max="16384" width="5.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
@@ -6556,7 +6934,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -6624,7 +7002,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6640,14 +7018,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -6658,7 +7036,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -6671,7 +7049,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6683,42 +7061,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DD8556-259C-4223-B758-7C936DE6D1CE}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE242"/>
-  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.15234375" style="31" customWidth="1"/>
-    <col min="3" max="3" width="11.3828125" style="31" customWidth="1"/>
-    <col min="4" max="4" width="9.3828125" style="31" customWidth="1"/>
-    <col min="5" max="5" width="8.15234375" style="31" customWidth="1"/>
-    <col min="6" max="6" width="6.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69140625" style="31" customWidth="1"/>
-    <col min="8" max="8" width="3.69140625" style="31" customWidth="1"/>
-    <col min="9" max="9" width="11.15234375" style="31" customWidth="1"/>
-    <col min="10" max="10" width="5.3046875" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3828125" style="32" customWidth="1"/>
-    <col min="13" max="13" width="11.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="31" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="31" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="31" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="31" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="31" customWidth="1"/>
+    <col min="10" max="10" width="5.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" style="32" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="31" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="44.15234375" customWidth="1"/>
-    <col min="16" max="16" width="8.3828125" style="32" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="52.15234375" style="31" customWidth="1"/>
-    <col min="18" max="18" width="5.15234375" style="32" customWidth="1"/>
+    <col min="15" max="15" width="44.140625" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" style="32" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="52.140625" style="31" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="32" customWidth="1"/>
     <col min="19" max="19" width="18" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.69140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.84375" style="31" customWidth="1"/>
-    <col min="22" max="22" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.69140625" style="80" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.15234375" style="80" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" style="31" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" style="72" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.140625" style="72" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -6813,14 +7191,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
         <v>2</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>551</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="62" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="42" t="s">
@@ -6908,14 +7286,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22">
         <v>3</v>
       </c>
       <c r="B3" s="41" t="s">
         <v>530</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D3" s="42" t="s">
@@ -7003,14 +7381,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>4</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>531</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D4" s="42" t="s">
@@ -7098,14 +7476,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <v>5</v>
       </c>
       <c r="B5" s="41" t="s">
         <v>532</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D5" s="42" t="s">
@@ -7193,14 +7571,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>6</v>
       </c>
       <c r="B6" s="41" t="s">
         <v>533</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D6" s="42" t="s">
@@ -7288,14 +7666,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>7</v>
       </c>
       <c r="B7" s="41" t="s">
         <v>539</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D7" s="42" t="s">
@@ -7383,14 +7761,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>8</v>
       </c>
       <c r="B8" s="41" t="s">
         <v>534</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D8" s="42" t="s">
@@ -7478,14 +7856,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22">
         <v>9</v>
       </c>
       <c r="B9" s="41" t="s">
         <v>535</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D9" s="42" t="s">
@@ -7573,14 +7951,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>10</v>
       </c>
       <c r="B10" s="41" t="s">
         <v>536</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D10" s="42" t="s">
@@ -7668,14 +8046,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
         <v>11</v>
       </c>
       <c r="B11" s="41" t="s">
         <v>540</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D11" s="42" t="s">
@@ -7763,14 +8141,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>12</v>
       </c>
       <c r="B12" s="41" t="s">
         <v>541</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D12" s="42" t="s">
@@ -7858,14 +8236,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22">
         <v>13</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>537</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D13" s="42" t="s">
@@ -7953,14 +8331,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22">
         <v>14</v>
       </c>
       <c r="B14" s="41" t="s">
         <v>542</v>
       </c>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D14" s="42" t="s">
@@ -8048,14 +8426,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22">
         <v>15</v>
       </c>
       <c r="B15" s="41" t="s">
         <v>543</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="63" t="s">
         <v>549</v>
       </c>
       <c r="D15" s="42" t="s">
@@ -8143,14 +8521,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22">
         <v>16</v>
       </c>
       <c r="B16" s="41" t="s">
         <v>553</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="63" t="s">
         <v>548</v>
       </c>
       <c r="D16" s="42" t="s">
@@ -8238,14 +8616,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22">
         <v>17</v>
       </c>
       <c r="B17" s="41" t="s">
         <v>441</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D17" s="42" t="s">
@@ -8333,14 +8711,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22">
         <v>18</v>
       </c>
       <c r="B18" s="41" t="s">
         <v>444</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D18" s="42" t="s">
@@ -8428,14 +8806,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22">
         <v>19</v>
       </c>
       <c r="B19" s="41" t="s">
         <v>446</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D19" s="42" t="s">
@@ -8523,14 +8901,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22">
         <v>20</v>
       </c>
       <c r="B20" s="41" t="s">
         <v>447</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D20" s="42" t="s">
@@ -8618,14 +8996,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22">
         <v>21</v>
       </c>
       <c r="B21" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D21" s="42" t="s">
@@ -8713,14 +9091,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22">
         <v>22</v>
       </c>
       <c r="B22" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="C22" s="71" t="s">
+      <c r="C22" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D22" s="42" t="s">
@@ -8808,14 +9186,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22">
         <v>23</v>
       </c>
       <c r="B23" s="41" t="s">
         <v>453</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D23" s="42" t="s">
@@ -8903,14 +9281,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22">
         <v>24</v>
       </c>
       <c r="B24" s="41" t="s">
         <v>456</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D24" s="42" t="s">
@@ -8998,14 +9376,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22">
         <v>25</v>
       </c>
       <c r="B25" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="63" t="s">
         <v>400</v>
       </c>
       <c r="D25" s="42" t="s">
@@ -9093,14 +9471,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22">
         <v>26</v>
       </c>
       <c r="B26" s="41" t="s">
         <v>460</v>
       </c>
-      <c r="C26" s="71" t="s">
+      <c r="C26" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D26" s="37" t="s">
@@ -9188,14 +9566,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
         <v>27</v>
       </c>
       <c r="B27" s="41" t="s">
         <v>463</v>
       </c>
-      <c r="C27" s="71" t="s">
+      <c r="C27" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D27" s="37" t="s">
@@ -9283,14 +9661,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22">
         <v>28</v>
       </c>
       <c r="B28" s="41" t="s">
         <v>464</v>
       </c>
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D28" s="37" t="s">
@@ -9378,14 +9756,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22">
         <v>29</v>
       </c>
       <c r="B29" s="41" t="s">
         <v>467</v>
       </c>
-      <c r="C29" s="71" t="s">
+      <c r="C29" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -9473,14 +9851,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22">
         <v>30</v>
       </c>
       <c r="B30" s="41" t="s">
         <v>469</v>
       </c>
-      <c r="C30" s="71" t="s">
+      <c r="C30" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D30" s="37" t="s">
@@ -9568,14 +9946,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22">
         <v>31</v>
       </c>
       <c r="B31" s="41" t="s">
         <v>465</v>
       </c>
-      <c r="C31" s="71" t="s">
+      <c r="C31" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D31" s="37" t="s">
@@ -9663,14 +10041,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22">
         <v>32</v>
       </c>
       <c r="B32" s="41" t="s">
         <v>471</v>
       </c>
-      <c r="C32" s="71" t="s">
+      <c r="C32" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D32" s="37" t="s">
@@ -9758,14 +10136,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22">
         <v>33</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>473</v>
       </c>
-      <c r="C33" s="71" t="s">
+      <c r="C33" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D33" s="37" t="s">
@@ -9853,14 +10231,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22">
         <v>34</v>
       </c>
       <c r="B34" s="41" t="s">
         <v>475</v>
       </c>
-      <c r="C34" s="71" t="s">
+      <c r="C34" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D34" s="37" t="s">
@@ -9948,14 +10326,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="22">
         <v>35</v>
       </c>
       <c r="B35" s="41" t="s">
         <v>476</v>
       </c>
-      <c r="C35" s="71" t="s">
+      <c r="C35" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D35" s="37" t="s">
@@ -10043,14 +10421,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22">
         <v>36</v>
       </c>
       <c r="B36" s="41" t="s">
         <v>477</v>
       </c>
-      <c r="C36" s="71" t="s">
+      <c r="C36" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -10138,14 +10516,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="22">
         <v>37</v>
       </c>
       <c r="B37" s="41" t="s">
         <v>478</v>
       </c>
-      <c r="C37" s="71" t="s">
+      <c r="C37" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D37" s="37" t="s">
@@ -10233,14 +10611,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
         <v>38</v>
       </c>
       <c r="B38" s="41" t="s">
         <v>480</v>
       </c>
-      <c r="C38" s="71" t="s">
+      <c r="C38" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D38" s="37" t="s">
@@ -10328,14 +10706,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22">
         <v>39</v>
       </c>
       <c r="B39" s="41" t="s">
         <v>481</v>
       </c>
-      <c r="C39" s="71" t="s">
+      <c r="C39" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D39" s="37" t="s">
@@ -10423,14 +10801,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22">
         <v>40</v>
       </c>
       <c r="B40" s="41" t="s">
         <v>482</v>
       </c>
-      <c r="C40" s="71" t="s">
+      <c r="C40" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D40" s="37" t="s">
@@ -10518,14 +10896,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="22">
         <v>41</v>
       </c>
       <c r="B41" s="41" t="s">
         <v>483</v>
       </c>
-      <c r="C41" s="71" t="s">
+      <c r="C41" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D41" s="37" t="s">
@@ -10613,14 +10991,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22">
         <v>42</v>
       </c>
       <c r="B42" s="41" t="s">
         <v>484</v>
       </c>
-      <c r="C42" s="71" t="s">
+      <c r="C42" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D42" s="37" t="s">
@@ -10708,14 +11086,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22">
         <v>43</v>
       </c>
       <c r="B43" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="C43" s="71" t="s">
+      <c r="C43" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D43" s="37" t="s">
@@ -10803,14 +11181,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22">
         <v>44</v>
       </c>
       <c r="B44" s="41" t="s">
         <v>487</v>
       </c>
-      <c r="C44" s="71" t="s">
+      <c r="C44" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D44" s="37" t="s">
@@ -10898,14 +11276,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22">
         <v>45</v>
       </c>
       <c r="B45" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="C45" s="71" t="s">
+      <c r="C45" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D45" s="37" t="s">
@@ -10993,14 +11371,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22">
         <v>46</v>
       </c>
       <c r="B46" s="41" t="s">
         <v>491</v>
       </c>
-      <c r="C46" s="71" t="s">
+      <c r="C46" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D46" s="37" t="s">
@@ -11088,14 +11466,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22">
         <v>47</v>
       </c>
       <c r="B47" s="41" t="s">
         <v>492</v>
       </c>
-      <c r="C47" s="71" t="s">
+      <c r="C47" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D47" s="37" t="s">
@@ -11183,14 +11561,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22">
         <v>48</v>
       </c>
       <c r="B48" s="41" t="s">
         <v>493</v>
       </c>
-      <c r="C48" s="71" t="s">
+      <c r="C48" s="63" t="s">
         <v>401</v>
       </c>
       <c r="D48" s="37" t="s">
@@ -11278,14 +11656,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22">
         <v>49</v>
       </c>
       <c r="B49" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="72" t="s">
+      <c r="C49" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D49" s="37" t="s">
@@ -11373,14 +11751,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22">
         <v>50</v>
       </c>
       <c r="B50" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C50" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D50" s="37" t="s">
@@ -11468,14 +11846,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="22">
         <v>51</v>
       </c>
       <c r="B51" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="72" t="s">
+      <c r="C51" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D51" s="37" t="s">
@@ -11563,14 +11941,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22">
         <v>52</v>
       </c>
       <c r="B52" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="72" t="s">
+      <c r="C52" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D52" s="37" t="s">
@@ -11658,14 +12036,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="22">
         <v>53</v>
       </c>
       <c r="B53" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="C53" s="72" t="s">
+      <c r="C53" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D53" s="37" t="s">
@@ -11753,14 +12131,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="22">
         <v>54</v>
       </c>
       <c r="B54" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="72" t="s">
+      <c r="C54" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D54" s="37" t="s">
@@ -11848,14 +12226,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="22">
         <v>55</v>
       </c>
       <c r="B55" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="72" t="s">
+      <c r="C55" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D55" s="37" t="s">
@@ -11943,14 +12321,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="22">
         <v>56</v>
       </c>
       <c r="B56" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="72" t="s">
+      <c r="C56" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D56" s="37" t="s">
@@ -12038,14 +12416,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22">
         <v>57</v>
       </c>
       <c r="B57" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C57" s="72" t="s">
+      <c r="C57" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D57" s="37" t="s">
@@ -12133,14 +12511,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="22">
         <v>58</v>
       </c>
       <c r="B58" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="72" t="s">
+      <c r="C58" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D58" s="37" t="s">
@@ -12228,14 +12606,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22">
         <v>59</v>
       </c>
       <c r="B59" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C59" s="72" t="s">
+      <c r="C59" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D59" s="37" t="s">
@@ -12323,14 +12701,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="22">
         <v>60</v>
       </c>
       <c r="B60" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="72" t="s">
+      <c r="C60" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D60" s="37" t="s">
@@ -12418,14 +12796,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22">
         <v>61</v>
       </c>
       <c r="B61" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="72" t="s">
+      <c r="C61" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D61" s="37" t="s">
@@ -12513,14 +12891,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22">
         <v>62</v>
       </c>
       <c r="B62" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="C62" s="72" t="s">
+      <c r="C62" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D62" s="37" t="s">
@@ -12608,14 +12986,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22">
         <v>63</v>
       </c>
       <c r="B63" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="72" t="s">
+      <c r="C63" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D63" s="37" t="s">
@@ -12703,14 +13081,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="22">
         <v>64</v>
       </c>
       <c r="B64" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="C64" s="72" t="s">
+      <c r="C64" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D64" s="37" t="s">
@@ -12798,14 +13176,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="22">
         <v>65</v>
       </c>
       <c r="B65" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="72" t="s">
+      <c r="C65" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D65" s="37" t="s">
@@ -12893,14 +13271,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="22">
         <v>66</v>
       </c>
       <c r="B66" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="72" t="s">
+      <c r="C66" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D66" s="37" t="s">
@@ -12988,14 +13366,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="22">
         <v>67</v>
       </c>
       <c r="B67" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="72" t="s">
+      <c r="C67" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D67" s="37" t="s">
@@ -13083,14 +13461,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="22">
         <v>68</v>
       </c>
       <c r="B68" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C68" s="72" t="s">
+      <c r="C68" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D68" s="37" t="s">
@@ -13178,14 +13556,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="22">
         <v>69</v>
       </c>
       <c r="B69" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="72" t="s">
+      <c r="C69" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D69" s="37" t="s">
@@ -13273,14 +13651,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="22">
         <v>70</v>
       </c>
       <c r="B70" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="C70" s="72" t="s">
+      <c r="C70" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D70" s="37" t="s">
@@ -13368,14 +13746,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="22">
         <v>71</v>
       </c>
       <c r="B71" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="C71" s="72" t="s">
+      <c r="C71" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D71" s="37" t="s">
@@ -13463,14 +13841,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="22">
         <v>72</v>
       </c>
       <c r="B72" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="72" t="s">
+      <c r="C72" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D72" s="37" t="s">
@@ -13558,14 +13936,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="22">
         <v>73</v>
       </c>
       <c r="B73" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="72" t="s">
+      <c r="C73" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D73" s="37" t="s">
@@ -13653,14 +14031,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22">
         <v>74</v>
       </c>
       <c r="B74" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="C74" s="72" t="s">
+      <c r="C74" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D74" s="37" t="s">
@@ -13748,14 +14126,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="22">
         <v>75</v>
       </c>
       <c r="B75" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="C75" s="72" t="s">
+      <c r="C75" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D75" s="37" t="s">
@@ -13843,14 +14221,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22">
         <v>76</v>
       </c>
       <c r="B76" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="C76" s="72" t="s">
+      <c r="C76" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D76" s="37" t="s">
@@ -13938,14 +14316,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="22">
         <v>77</v>
       </c>
       <c r="B77" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="C77" s="72" t="s">
+      <c r="C77" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D77" s="37" t="s">
@@ -14033,14 +14411,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22">
         <v>78</v>
       </c>
       <c r="B78" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="C78" s="72" t="s">
+      <c r="C78" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D78" s="37" t="s">
@@ -14128,14 +14506,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22">
         <v>79</v>
       </c>
       <c r="B79" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="C79" s="72" t="s">
+      <c r="C79" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D79" s="37" t="s">
@@ -14223,14 +14601,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="22">
         <v>80</v>
       </c>
       <c r="B80" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="C80" s="72" t="s">
+      <c r="C80" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D80" s="37" t="s">
@@ -14318,14 +14696,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="22">
         <v>81</v>
       </c>
       <c r="B81" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="C81" s="72" t="s">
+      <c r="C81" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D81" s="37" t="s">
@@ -14413,14 +14791,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="22">
         <v>82</v>
       </c>
       <c r="B82" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C82" s="72" t="s">
+      <c r="C82" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D82" s="37" t="s">
@@ -14508,14 +14886,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="22">
         <v>83</v>
       </c>
       <c r="B83" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="C83" s="72" t="s">
+      <c r="C83" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D83" s="37" t="s">
@@ -14603,14 +14981,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="22">
         <v>84</v>
       </c>
       <c r="B84" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="C84" s="72" t="s">
+      <c r="C84" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D84" s="37" t="s">
@@ -14698,14 +15076,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="22">
         <v>85</v>
       </c>
       <c r="B85" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="C85" s="72" t="s">
+      <c r="C85" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D85" s="37" t="s">
@@ -14793,14 +15171,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="22">
         <v>86</v>
       </c>
       <c r="B86" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="C86" s="72" t="s">
+      <c r="C86" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D86" s="37" t="s">
@@ -14888,14 +15266,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="22">
         <v>87</v>
       </c>
       <c r="B87" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C87" s="72" t="s">
+      <c r="C87" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D87" s="37" t="s">
@@ -14983,14 +15361,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="22">
         <v>88</v>
       </c>
       <c r="B88" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C88" s="72" t="s">
+      <c r="C88" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D88" s="37" t="s">
@@ -15078,14 +15456,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22">
         <v>89</v>
       </c>
       <c r="B89" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="72" t="s">
+      <c r="C89" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D89" s="37" t="s">
@@ -15173,14 +15551,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="22">
         <v>90</v>
       </c>
       <c r="B90" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="C90" s="72" t="s">
+      <c r="C90" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D90" s="37" t="s">
@@ -15268,14 +15646,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="22">
         <v>91</v>
       </c>
       <c r="B91" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="C91" s="72" t="s">
+      <c r="C91" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D91" s="37" t="s">
@@ -15363,14 +15741,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="22">
         <v>92</v>
       </c>
       <c r="B92" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C92" s="72" t="s">
+      <c r="C92" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D92" s="37" t="s">
@@ -15458,14 +15836,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22">
         <v>93</v>
       </c>
       <c r="B93" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="C93" s="72" t="s">
+      <c r="C93" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D93" s="37" t="s">
@@ -15553,14 +15931,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="22">
         <v>94</v>
       </c>
       <c r="B94" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="C94" s="72" t="s">
+      <c r="C94" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D94" s="37" t="s">
@@ -15648,14 +16026,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="22">
         <v>95</v>
       </c>
       <c r="B95" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="C95" s="72" t="s">
+      <c r="C95" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D95" s="37" t="s">
@@ -15743,14 +16121,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="22">
         <v>96</v>
       </c>
       <c r="B96" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="C96" s="72" t="s">
+      <c r="C96" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D96" s="37" t="s">
@@ -15838,14 +16216,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="22">
         <v>97</v>
       </c>
       <c r="B97" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="C97" s="72" t="s">
+      <c r="C97" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D97" s="37" t="s">
@@ -15933,14 +16311,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="22">
         <v>98</v>
       </c>
       <c r="B98" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="C98" s="72" t="s">
+      <c r="C98" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D98" s="37" t="s">
@@ -16028,14 +16406,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="22">
         <v>99</v>
       </c>
       <c r="B99" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="C99" s="72" t="s">
+      <c r="C99" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D99" s="37" t="s">
@@ -16123,14 +16501,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="22">
         <v>100</v>
       </c>
       <c r="B100" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="C100" s="72" t="s">
+      <c r="C100" s="64" t="s">
         <v>418</v>
       </c>
       <c r="D100" s="37" t="s">
@@ -16218,14 +16596,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="22">
         <v>101</v>
       </c>
       <c r="B101" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="C101" s="72" t="s">
+      <c r="C101" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D101" s="37" t="s">
@@ -16313,14 +16691,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="22">
         <v>102</v>
       </c>
       <c r="B102" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="C102" s="72" t="s">
+      <c r="C102" s="64" t="s">
         <v>418</v>
       </c>
       <c r="D102" s="37" t="s">
@@ -16408,14 +16786,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="22">
         <v>103</v>
       </c>
       <c r="B103" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="C103" s="72" t="s">
+      <c r="C103" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D103" s="37" t="s">
@@ -16503,14 +16881,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="22">
         <v>104</v>
       </c>
       <c r="B104" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="C104" s="72" t="s">
+      <c r="C104" s="64" t="s">
         <v>418</v>
       </c>
       <c r="D104" s="37" t="s">
@@ -16598,14 +16976,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="22">
         <v>105</v>
       </c>
       <c r="B105" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="C105" s="72" t="s">
+      <c r="C105" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D105" s="37" t="s">
@@ -16693,14 +17071,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="22">
         <v>106</v>
       </c>
       <c r="B106" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="C106" s="72" t="s">
+      <c r="C106" s="64" t="s">
         <v>418</v>
       </c>
       <c r="D106" s="37" t="s">
@@ -16788,14 +17166,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="22">
         <v>107</v>
       </c>
       <c r="B107" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="C107" s="72" t="s">
+      <c r="C107" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D107" s="37" t="s">
@@ -16883,14 +17261,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="22">
         <v>108</v>
       </c>
       <c r="B108" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="C108" s="72" t="s">
+      <c r="C108" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D108" s="37" t="s">
@@ -16978,14 +17356,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="22">
         <v>109</v>
       </c>
       <c r="B109" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="C109" s="72" t="s">
+      <c r="C109" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D109" s="37" t="s">
@@ -17073,14 +17451,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="22">
         <v>110</v>
       </c>
       <c r="B110" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="C110" s="72" t="s">
+      <c r="C110" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D110" s="37" t="s">
@@ -17168,14 +17546,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="22">
         <v>111</v>
       </c>
       <c r="B111" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="C111" s="72" t="s">
+      <c r="C111" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D111" s="37" t="s">
@@ -17263,14 +17641,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="22">
         <v>112</v>
       </c>
       <c r="B112" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="C112" s="72" t="s">
+      <c r="C112" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D112" s="37" t="s">
@@ -17358,14 +17736,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="22">
         <v>113</v>
       </c>
       <c r="B113" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="C113" s="72" t="s">
+      <c r="C113" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D113" s="37" t="s">
@@ -17453,14 +17831,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="22">
         <v>114</v>
       </c>
       <c r="B114" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="C114" s="72" t="s">
+      <c r="C114" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D114" s="37" t="s">
@@ -17548,14 +17926,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="22">
         <v>115</v>
       </c>
       <c r="B115" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="C115" s="72" t="s">
+      <c r="C115" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D115" s="37" t="s">
@@ -17643,14 +18021,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="22">
         <v>116</v>
       </c>
       <c r="B116" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="C116" s="72" t="s">
+      <c r="C116" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D116" s="37" t="s">
@@ -17738,14 +18116,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="22">
         <v>117</v>
       </c>
       <c r="B117" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C117" s="72" t="s">
+      <c r="C117" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D117" s="37" t="s">
@@ -17833,14 +18211,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="22">
         <v>118</v>
       </c>
       <c r="B118" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="C118" s="72" t="s">
+      <c r="C118" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D118" s="37" t="s">
@@ -17928,14 +18306,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="22">
         <v>119</v>
       </c>
       <c r="B119" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="72" t="s">
+      <c r="C119" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D119" s="37" t="s">
@@ -18023,14 +18401,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="22">
         <v>120</v>
       </c>
       <c r="B120" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="C120" s="72" t="s">
+      <c r="C120" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D120" s="37" t="s">
@@ -18118,14 +18496,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="22">
         <v>121</v>
       </c>
       <c r="B121" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="C121" s="72" t="s">
+      <c r="C121" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D121" s="37" t="s">
@@ -18213,14 +18591,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="22">
         <v>122</v>
       </c>
       <c r="B122" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="C122" s="72" t="s">
+      <c r="C122" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D122" s="37" t="s">
@@ -18308,14 +18686,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="22">
         <v>123</v>
       </c>
       <c r="B123" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="C123" s="72" t="s">
+      <c r="C123" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D123" s="37" t="s">
@@ -18403,14 +18781,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="22">
         <v>124</v>
       </c>
       <c r="B124" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="C124" s="72" t="s">
+      <c r="C124" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D124" s="37" t="s">
@@ -18498,14 +18876,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="22">
         <v>125</v>
       </c>
       <c r="B125" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="C125" s="72" t="s">
+      <c r="C125" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D125" s="37" t="s">
@@ -18593,14 +18971,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="22">
         <v>126</v>
       </c>
       <c r="B126" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="C126" s="72" t="s">
+      <c r="C126" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D126" s="37" t="s">
@@ -18688,14 +19066,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="22">
         <v>127</v>
       </c>
       <c r="B127" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="C127" s="72" t="s">
+      <c r="C127" s="64" t="s">
         <v>417</v>
       </c>
       <c r="D127" s="37" t="s">
@@ -18783,14 +19161,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="22">
         <v>128</v>
       </c>
       <c r="B128" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="C128" s="72" t="s">
+      <c r="C128" s="64" t="s">
         <v>418</v>
       </c>
       <c r="D128" s="37" t="s">
@@ -18878,14 +19256,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="22">
         <v>129</v>
       </c>
       <c r="B129" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="C129" s="72" t="s">
+      <c r="C129" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D129" s="37" t="s">
@@ -18973,14 +19351,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="22">
         <v>130</v>
       </c>
       <c r="B130" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C130" s="72" t="s">
+      <c r="C130" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D130" s="37" t="s">
@@ -19068,14 +19446,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="22">
         <v>131</v>
       </c>
       <c r="B131" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="C131" s="72" t="s">
+      <c r="C131" s="64" t="s">
         <v>413</v>
       </c>
       <c r="D131" s="37" t="s">
@@ -19163,14 +19541,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="22">
         <v>132</v>
       </c>
       <c r="B132" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="C132" s="72" t="s">
+      <c r="C132" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D132" s="37" t="s">
@@ -19258,14 +19636,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="22">
         <v>133</v>
       </c>
       <c r="B133" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="C133" s="72" t="s">
+      <c r="C133" s="64" t="s">
         <v>420</v>
       </c>
       <c r="D133" s="37" t="s">
@@ -19353,14 +19731,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="22">
         <v>134</v>
       </c>
       <c r="B134" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="C134" s="72" t="s">
+      <c r="C134" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D134" s="37" t="s">
@@ -19448,14 +19826,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="22">
         <v>135</v>
       </c>
       <c r="B135" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="C135" s="72" t="s">
+      <c r="C135" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D135" s="37" t="s">
@@ -19543,14 +19921,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="22">
         <v>136</v>
       </c>
       <c r="B136" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="C136" s="72" t="s">
+      <c r="C136" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D136" s="37" t="s">
@@ -19638,14 +20016,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="22">
         <v>137</v>
       </c>
       <c r="B137" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="C137" s="72" t="s">
+      <c r="C137" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D137" s="37" t="s">
@@ -19733,14 +20111,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="22">
         <v>138</v>
       </c>
       <c r="B138" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="C138" s="72" t="s">
+      <c r="C138" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D138" s="37" t="s">
@@ -19828,14 +20206,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="22">
         <v>139</v>
       </c>
       <c r="B139" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="C139" s="72" t="s">
+      <c r="C139" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D139" s="37" t="s">
@@ -19923,14 +20301,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="22">
         <v>140</v>
       </c>
       <c r="B140" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C140" s="72" t="s">
+      <c r="C140" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D140" s="37" t="s">
@@ -20018,14 +20396,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="22">
         <v>141</v>
       </c>
       <c r="B141" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="C141" s="72" t="s">
+      <c r="C141" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D141" s="37" t="s">
@@ -20113,14 +20491,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="22">
         <v>142</v>
       </c>
       <c r="B142" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="C142" s="72" t="s">
+      <c r="C142" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D142" s="37" t="s">
@@ -20208,14 +20586,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="22">
         <v>143</v>
       </c>
       <c r="B143" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="C143" s="72" t="s">
+      <c r="C143" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D143" s="37" t="s">
@@ -20303,14 +20681,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="22">
         <v>144</v>
       </c>
       <c r="B144" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="C144" s="72" t="s">
+      <c r="C144" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D144" s="37" t="s">
@@ -20398,14 +20776,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="22">
         <v>145</v>
       </c>
       <c r="B145" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="C145" s="72" t="s">
+      <c r="C145" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D145" s="37" t="s">
@@ -20493,14 +20871,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="22">
         <v>146</v>
       </c>
       <c r="B146" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="C146" s="72" t="s">
+      <c r="C146" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D146" s="37" t="s">
@@ -20588,14 +20966,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="22">
         <v>147</v>
       </c>
       <c r="B147" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="C147" s="72" t="s">
+      <c r="C147" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D147" s="37" t="s">
@@ -20683,14 +21061,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="22">
         <v>148</v>
       </c>
       <c r="B148" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="C148" s="72" t="s">
+      <c r="C148" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D148" s="37" t="s">
@@ -20778,14 +21156,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="22">
         <v>149</v>
       </c>
       <c r="B149" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="C149" s="72" t="s">
+      <c r="C149" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D149" s="37" t="s">
@@ -20873,14 +21251,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="22">
         <v>150</v>
       </c>
       <c r="B150" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="C150" s="72" t="s">
+      <c r="C150" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D150" s="37" t="s">
@@ -20968,14 +21346,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="22">
         <v>151</v>
       </c>
       <c r="B151" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="C151" s="72" t="s">
+      <c r="C151" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D151" s="37" t="s">
@@ -21063,14 +21441,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="22">
         <v>152</v>
       </c>
       <c r="B152" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="C152" s="72" t="s">
+      <c r="C152" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D152" s="37" t="s">
@@ -21158,14 +21536,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="22">
         <v>153</v>
       </c>
       <c r="B153" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="C153" s="72" t="s">
+      <c r="C153" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D153" s="37" t="s">
@@ -21253,14 +21631,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="22">
         <v>154</v>
       </c>
       <c r="B154" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="C154" s="72" t="s">
+      <c r="C154" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D154" s="37" t="s">
@@ -21348,14 +21726,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="22">
         <v>155</v>
       </c>
       <c r="B155" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="C155" s="72" t="s">
+      <c r="C155" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D155" s="37" t="s">
@@ -21443,14 +21821,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="22">
         <v>156</v>
       </c>
       <c r="B156" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="C156" s="72" t="s">
+      <c r="C156" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D156" s="37" t="s">
@@ -21538,14 +21916,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="22">
         <v>157</v>
       </c>
       <c r="B157" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="C157" s="72" t="s">
+      <c r="C157" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D157" s="37" t="s">
@@ -21633,14 +22011,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="22">
         <v>158</v>
       </c>
       <c r="B158" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="C158" s="72" t="s">
+      <c r="C158" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D158" s="37" t="s">
@@ -21728,14 +22106,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="22">
         <v>159</v>
       </c>
       <c r="B159" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="C159" s="72" t="s">
+      <c r="C159" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D159" s="37" t="s">
@@ -21823,14 +22201,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="22">
         <v>160</v>
       </c>
       <c r="B160" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="C160" s="72" t="s">
+      <c r="C160" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D160" s="37" t="s">
@@ -21918,14 +22296,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="22">
         <v>161</v>
       </c>
       <c r="B161" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="C161" s="72" t="s">
+      <c r="C161" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D161" s="37" t="s">
@@ -22013,14 +22391,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="22">
         <v>162</v>
       </c>
       <c r="B162" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C162" s="72" t="s">
+      <c r="C162" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D162" s="37" t="s">
@@ -22108,14 +22486,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="22">
         <v>163</v>
       </c>
       <c r="B163" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="C163" s="72" t="s">
+      <c r="C163" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D163" s="37" t="s">
@@ -22203,14 +22581,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="22">
         <v>164</v>
       </c>
       <c r="B164" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="C164" s="72" t="s">
+      <c r="C164" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D164" s="37" t="s">
@@ -22298,14 +22676,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="22">
         <v>165</v>
       </c>
       <c r="B165" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="C165" s="72" t="s">
+      <c r="C165" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D165" s="37" t="s">
@@ -22393,14 +22771,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="22">
         <v>166</v>
       </c>
       <c r="B166" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="C166" s="72" t="s">
+      <c r="C166" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D166" s="37" t="s">
@@ -22488,14 +22866,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="22">
         <v>167</v>
       </c>
       <c r="B167" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="C167" s="72" t="s">
+      <c r="C167" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D167" s="37" t="s">
@@ -22583,14 +22961,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="22">
         <v>168</v>
       </c>
       <c r="B168" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="C168" s="72" t="s">
+      <c r="C168" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D168" s="37" t="s">
@@ -22678,14 +23056,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="22">
         <v>169</v>
       </c>
       <c r="B169" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="C169" s="72" t="s">
+      <c r="C169" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D169" s="37" t="s">
@@ -22773,14 +23151,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="22">
         <v>170</v>
       </c>
       <c r="B170" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="C170" s="72" t="s">
+      <c r="C170" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D170" s="37" t="s">
@@ -22868,14 +23246,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="22">
         <v>171</v>
       </c>
       <c r="B171" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="C171" s="72" t="s">
+      <c r="C171" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D171" s="37" t="s">
@@ -22963,14 +23341,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="22">
         <v>172</v>
       </c>
       <c r="B172" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="C172" s="72" t="s">
+      <c r="C172" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D172" s="37" t="s">
@@ -23058,14 +23436,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="22">
         <v>173</v>
       </c>
       <c r="B173" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="C173" s="72" t="s">
+      <c r="C173" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D173" s="37" t="s">
@@ -23153,14 +23531,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="22">
         <v>174</v>
       </c>
       <c r="B174" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="C174" s="72" t="s">
+      <c r="C174" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D174" s="37" t="s">
@@ -23248,14 +23626,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="22">
         <v>175</v>
       </c>
       <c r="B175" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="C175" s="72" t="s">
+      <c r="C175" s="64" t="s">
         <v>399</v>
       </c>
       <c r="D175" s="37" t="s">
@@ -23343,14 +23721,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="22">
         <v>176</v>
       </c>
       <c r="B176" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="C176" s="72" t="s">
+      <c r="C176" s="64" t="s">
         <v>414</v>
       </c>
       <c r="D176" s="37" t="s">
@@ -23438,14 +23816,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="22">
         <v>177</v>
       </c>
       <c r="B177" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="C177" s="72" t="s">
+      <c r="C177" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D177" s="37" t="s">
@@ -23533,14 +23911,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="22">
         <v>178</v>
       </c>
       <c r="B178" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="C178" s="72" t="s">
+      <c r="C178" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D178" s="37" t="s">
@@ -23628,14 +24006,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="22">
         <v>179</v>
       </c>
       <c r="B179" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="C179" s="72" t="s">
+      <c r="C179" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D179" s="37" t="s">
@@ -23723,14 +24101,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="22">
         <v>180</v>
       </c>
       <c r="B180" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="C180" s="72" t="s">
+      <c r="C180" s="64" t="s">
         <v>415</v>
       </c>
       <c r="D180" s="37" t="s">
@@ -23818,14 +24196,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="22">
         <v>181</v>
       </c>
       <c r="B181" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="C181" s="72" t="s">
+      <c r="C181" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D181" s="37" t="s">
@@ -23913,14 +24291,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="22">
         <v>182</v>
       </c>
       <c r="B182" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="C182" s="72" t="s">
+      <c r="C182" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D182" s="37" t="s">
@@ -24008,14 +24386,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="22">
         <v>183</v>
       </c>
       <c r="B183" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="C183" s="72" t="s">
+      <c r="C183" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D183" s="37" t="s">
@@ -24103,14 +24481,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="22">
         <v>184</v>
       </c>
       <c r="B184" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C184" s="72" t="s">
+      <c r="C184" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D184" s="37" t="s">
@@ -24198,14 +24576,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="22">
         <v>185</v>
       </c>
       <c r="B185" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="C185" s="72" t="s">
+      <c r="C185" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D185" s="37" t="s">
@@ -24293,14 +24671,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="22">
         <v>186</v>
       </c>
       <c r="B186" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="C186" s="72" t="s">
+      <c r="C186" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D186" s="37" t="s">
@@ -24388,14 +24766,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="22">
         <v>187</v>
       </c>
       <c r="B187" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C187" s="72" t="s">
+      <c r="C187" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D187" s="37" t="s">
@@ -24483,14 +24861,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="22">
         <v>188</v>
       </c>
       <c r="B188" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="C188" s="72" t="s">
+      <c r="C188" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D188" s="37" t="s">
@@ -24578,14 +24956,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="22">
         <v>189</v>
       </c>
       <c r="B189" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="C189" s="72" t="s">
+      <c r="C189" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D189" s="37" t="s">
@@ -24673,14 +25051,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="22">
         <v>190</v>
       </c>
       <c r="B190" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="C190" s="72" t="s">
+      <c r="C190" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D190" s="37" t="s">
@@ -24768,14 +25146,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="22">
         <v>191</v>
       </c>
       <c r="B191" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="C191" s="72" t="s">
+      <c r="C191" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D191" s="37" t="s">
@@ -24863,14 +25241,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="22">
         <v>192</v>
       </c>
       <c r="B192" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="C192" s="72" t="s">
+      <c r="C192" s="64" t="s">
         <v>419</v>
       </c>
       <c r="D192" s="37" t="s">
@@ -24958,14 +25336,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="22">
         <v>193</v>
       </c>
       <c r="B193" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="C193" s="73" t="s">
+      <c r="C193" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D193" s="37" t="s">
@@ -25053,14 +25431,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="22">
         <v>194</v>
       </c>
       <c r="B194" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="C194" s="73" t="s">
+      <c r="C194" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D194" s="37" t="s">
@@ -25148,14 +25526,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="22">
         <v>195</v>
       </c>
       <c r="B195" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="C195" s="73" t="s">
+      <c r="C195" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D195" s="37" t="s">
@@ -25243,14 +25621,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="22">
         <v>196</v>
       </c>
       <c r="B196" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="C196" s="73" t="s">
+      <c r="C196" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D196" s="37" t="s">
@@ -25338,14 +25716,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="22">
         <v>197</v>
       </c>
       <c r="B197" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="C197" s="73" t="s">
+      <c r="C197" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D197" s="37" t="s">
@@ -25433,14 +25811,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="22">
         <v>198</v>
       </c>
       <c r="B198" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="C198" s="73" t="s">
+      <c r="C198" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D198" s="37" t="s">
@@ -25528,14 +25906,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="22">
         <v>199</v>
       </c>
       <c r="B199" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="C199" s="73" t="s">
+      <c r="C199" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D199" s="37" t="s">
@@ -25623,14 +26001,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="22">
         <v>200</v>
       </c>
       <c r="B200" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="C200" s="73" t="s">
+      <c r="C200" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D200" s="37" t="s">
@@ -25718,14 +26096,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="22">
         <v>201</v>
       </c>
       <c r="B201" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="C201" s="73" t="s">
+      <c r="C201" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D201" s="37" t="s">
@@ -25813,14 +26191,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="22">
         <v>202</v>
       </c>
       <c r="B202" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="C202" s="73" t="s">
+      <c r="C202" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D202" s="37" t="s">
@@ -25908,14 +26286,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="22">
         <v>203</v>
       </c>
       <c r="B203" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="C203" s="73" t="s">
+      <c r="C203" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D203" s="37" t="s">
@@ -26003,14 +26381,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="22">
         <v>204</v>
       </c>
       <c r="B204" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="C204" s="73" t="s">
+      <c r="C204" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D204" s="37" t="s">
@@ -26098,14 +26476,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="22">
         <v>205</v>
       </c>
       <c r="B205" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="C205" s="73" t="s">
+      <c r="C205" s="65" t="s">
         <v>416</v>
       </c>
       <c r="D205" s="37" t="s">
@@ -26193,14 +26571,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="22">
         <v>206</v>
       </c>
       <c r="B206" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="C206" s="73" t="s">
+      <c r="C206" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D206" s="37" t="s">
@@ -26288,14 +26666,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="22">
         <v>207</v>
       </c>
       <c r="B207" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="C207" s="73" t="s">
+      <c r="C207" s="65" t="s">
         <v>415</v>
       </c>
       <c r="D207" s="37" t="s">
@@ -26383,14 +26761,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="22">
         <v>208</v>
       </c>
       <c r="B208" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="C208" s="73" t="s">
+      <c r="C208" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D208" s="37" t="s">
@@ -26478,14 +26856,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="22">
         <v>209</v>
       </c>
       <c r="B209" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="C209" s="73" t="s">
+      <c r="C209" s="65" t="s">
         <v>414</v>
       </c>
       <c r="D209" s="37" t="s">
@@ -26573,14 +26951,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="22">
         <v>210</v>
       </c>
       <c r="B210" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="C210" s="73" t="s">
+      <c r="C210" s="65" t="s">
         <v>416</v>
       </c>
       <c r="D210" s="37" t="s">
@@ -26668,14 +27046,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="22">
         <v>211</v>
       </c>
       <c r="B211" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="C211" s="73" t="s">
+      <c r="C211" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D211" s="37" t="s">
@@ -26763,14 +27141,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="22">
         <v>212</v>
       </c>
       <c r="B212" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="C212" s="73" t="s">
+      <c r="C212" s="65" t="s">
         <v>413</v>
       </c>
       <c r="D212" s="37" t="s">
@@ -26858,14 +27236,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="22">
         <v>213</v>
       </c>
       <c r="B213" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="C213" s="73" t="s">
+      <c r="C213" s="65" t="s">
         <v>416</v>
       </c>
       <c r="D213" s="37" t="s">
@@ -26953,14 +27331,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="22">
         <v>214</v>
       </c>
       <c r="B214" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="C214" s="73" t="s">
+      <c r="C214" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D214" s="37" t="s">
@@ -27048,14 +27426,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="22">
         <v>215</v>
       </c>
       <c r="B215" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="C215" s="73" t="s">
+      <c r="C215" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D215" s="37" t="s">
@@ -27143,14 +27521,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="22">
         <v>216</v>
       </c>
       <c r="B216" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="C216" s="73" t="s">
+      <c r="C216" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D216" s="37" t="s">
@@ -27238,14 +27616,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="22">
         <v>217</v>
       </c>
       <c r="B217" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="C217" s="73" t="s">
+      <c r="C217" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D217" s="37" t="s">
@@ -27333,14 +27711,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="22">
         <v>218</v>
       </c>
       <c r="B218" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="C218" s="73" t="s">
+      <c r="C218" s="65" t="s">
         <v>413</v>
       </c>
       <c r="D218" s="37" t="s">
@@ -27428,14 +27806,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="22">
         <v>219</v>
       </c>
       <c r="B219" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="C219" s="73" t="s">
+      <c r="C219" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D219" s="37" t="s">
@@ -27523,14 +27901,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="22">
         <v>220</v>
       </c>
       <c r="B220" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="C220" s="73" t="s">
+      <c r="C220" s="65" t="s">
         <v>399</v>
       </c>
       <c r="D220" s="37" t="s">
@@ -27618,14 +27996,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="22">
         <v>221</v>
       </c>
       <c r="B221" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="C221" s="73" t="s">
+      <c r="C221" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D221" s="37" t="s">
@@ -27713,14 +28091,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="22">
         <v>222</v>
       </c>
       <c r="B222" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="C222" s="73" t="s">
+      <c r="C222" s="65" t="s">
         <v>419</v>
       </c>
       <c r="D222" s="37" t="s">
@@ -27808,14 +28186,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="22">
         <v>223</v>
       </c>
       <c r="B223" s="41" t="s">
         <v>248</v>
       </c>
-      <c r="C223" s="73" t="s">
+      <c r="C223" s="65" t="s">
         <v>416</v>
       </c>
       <c r="D223" s="37" t="s">
@@ -27903,14 +28281,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="22">
         <v>224</v>
       </c>
       <c r="B224" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="C224" s="73" t="s">
+      <c r="C224" s="65" t="s">
         <v>416</v>
       </c>
       <c r="D224" s="37" t="s">
@@ -27998,14 +28376,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="22">
         <v>225</v>
       </c>
       <c r="B225" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="C225" s="72" t="s">
+      <c r="C225" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D225" s="37" t="s">
@@ -28093,14 +28471,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="22">
         <v>226</v>
       </c>
       <c r="B226" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="C226" s="72" t="s">
+      <c r="C226" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D226" s="37" t="s">
@@ -28188,14 +28566,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="22">
         <v>227</v>
       </c>
       <c r="B227" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="C227" s="72" t="s">
+      <c r="C227" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D227" s="37" t="s">
@@ -28283,14 +28661,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="22">
         <v>228</v>
       </c>
       <c r="B228" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="C228" s="72" t="s">
+      <c r="C228" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D228" s="37" t="s">
@@ -28378,14 +28756,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="22">
         <v>229</v>
       </c>
       <c r="B229" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="C229" s="72" t="s">
+      <c r="C229" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D229" s="37" t="s">
@@ -28473,14 +28851,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="22">
         <v>230</v>
       </c>
       <c r="B230" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="C230" s="72" t="s">
+      <c r="C230" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D230" s="37" t="s">
@@ -28568,14 +28946,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="22">
         <v>231</v>
       </c>
       <c r="B231" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="C231" s="72" t="s">
+      <c r="C231" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D231" s="37" t="s">
@@ -28663,14 +29041,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="22">
         <v>232</v>
       </c>
       <c r="B232" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="C232" s="72" t="s">
+      <c r="C232" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D232" s="37" t="s">
@@ -28758,14 +29136,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="22">
         <v>233</v>
       </c>
       <c r="B233" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="C233" s="72" t="s">
+      <c r="C233" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D233" s="37" t="s">
@@ -28853,14 +29231,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="22">
         <v>234</v>
       </c>
       <c r="B234" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="C234" s="72" t="s">
+      <c r="C234" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D234" s="37" t="s">
@@ -28948,14 +29326,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="22">
         <v>235</v>
       </c>
       <c r="B235" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="C235" s="72" t="s">
+      <c r="C235" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D235" s="37" t="s">
@@ -29043,14 +29421,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="22">
         <v>236</v>
       </c>
       <c r="B236" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="C236" s="72" t="s">
+      <c r="C236" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D236" s="37" t="s">
@@ -29138,14 +29516,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:31" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:31" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="22">
         <v>237</v>
       </c>
       <c r="B237" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="C237" s="72" t="s">
+      <c r="C237" s="64" t="s">
         <v>416</v>
       </c>
       <c r="D237" s="37" t="s">
@@ -29233,69 +29611,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="22">
         <v>238</v>
       </c>
-      <c r="B238" s="81" t="s">
+      <c r="B238" s="73" t="s">
+        <v>729</v>
+      </c>
+      <c r="C238" s="80" t="s">
+        <v>763</v>
+      </c>
+      <c r="D238" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E238" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F238" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="G238" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H238" s="74" t="s">
+        <v>385</v>
+      </c>
+      <c r="I238" s="75" t="s">
+        <v>730</v>
+      </c>
+      <c r="J238" s="74" t="s">
+        <v>731</v>
+      </c>
+      <c r="K238" s="75" t="s">
+        <v>732</v>
+      </c>
+      <c r="L238" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M238" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N238" s="76" t="s">
+        <v>386</v>
+      </c>
+      <c r="O238" s="75" t="s">
         <v>733</v>
       </c>
-      <c r="C238" s="88" t="s">
-        <v>729</v>
-      </c>
-      <c r="D238" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E238" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F238" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G238" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="H238" s="82" t="s">
-        <v>385</v>
-      </c>
-      <c r="I238" s="83" t="s">
-        <v>734</v>
-      </c>
-      <c r="J238" s="82" t="s">
-        <v>735</v>
-      </c>
-      <c r="K238" s="83" t="s">
-        <v>736</v>
-      </c>
-      <c r="L238" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="M238" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="N238" s="84" t="s">
-        <v>386</v>
-      </c>
-      <c r="O238" s="83" t="s">
-        <v>737</v>
-      </c>
-      <c r="P238" s="85" t="str">
+      <c r="P238" s="77" t="str">
         <f t="shared" ref="P238:P242" si="0">IF(Q238="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Q238" s="86" t="s">
-        <v>738</v>
-      </c>
-      <c r="R238" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="S238" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="T238" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="U238" s="87" t="s">
+      <c r="Q238" s="78" t="s">
+        <v>734</v>
+      </c>
+      <c r="R238" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S238" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="T238" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="U238" s="79" t="s">
         <v>1</v>
       </c>
       <c r="V238" s="37" t="s">
@@ -29329,15 +29707,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="22">
         <v>239</v>
       </c>
-      <c r="B239" s="81" t="s">
-        <v>739</v>
-      </c>
-      <c r="C239" s="88" t="s">
-        <v>729</v>
+      <c r="B239" s="73" t="s">
+        <v>735</v>
+      </c>
+      <c r="C239" s="80" t="s">
+        <v>763</v>
       </c>
       <c r="D239" s="37" t="s">
         <v>1</v>
@@ -29351,17 +29729,17 @@
       <c r="G239" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H239" s="82" t="s">
+      <c r="H239" s="74" t="s">
         <v>385</v>
       </c>
-      <c r="I239" s="83" t="s">
-        <v>734</v>
-      </c>
-      <c r="J239" s="82" t="s">
-        <v>735</v>
-      </c>
-      <c r="K239" s="83" t="s">
-        <v>740</v>
+      <c r="I239" s="75" t="s">
+        <v>730</v>
+      </c>
+      <c r="J239" s="74" t="s">
+        <v>731</v>
+      </c>
+      <c r="K239" s="75" t="s">
+        <v>736</v>
       </c>
       <c r="L239" s="30" t="s">
         <v>1</v>
@@ -29369,29 +29747,29 @@
       <c r="M239" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="N239" s="84" t="s">
+      <c r="N239" s="76" t="s">
         <v>386</v>
       </c>
-      <c r="O239" s="83" t="s">
-        <v>741</v>
-      </c>
-      <c r="P239" s="85" t="str">
+      <c r="O239" s="75" t="s">
+        <v>737</v>
+      </c>
+      <c r="P239" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q239" s="86" t="s">
-        <v>742</v>
-      </c>
-      <c r="R239" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="S239" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="T239" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="U239" s="87" t="s">
+      <c r="Q239" s="78" t="s">
+        <v>738</v>
+      </c>
+      <c r="R239" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S239" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="T239" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="U239" s="79" t="s">
         <v>1</v>
       </c>
       <c r="V239" s="37" t="s">
@@ -29425,15 +29803,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="22">
         <v>240</v>
       </c>
-      <c r="B240" s="81" t="s">
-        <v>743</v>
-      </c>
-      <c r="C240" s="88" t="s">
-        <v>729</v>
+      <c r="B240" s="73" t="s">
+        <v>739</v>
+      </c>
+      <c r="C240" s="80" t="s">
+        <v>763</v>
       </c>
       <c r="D240" s="37" t="s">
         <v>1</v>
@@ -29447,17 +29825,17 @@
       <c r="G240" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H240" s="82" t="s">
+      <c r="H240" s="74" t="s">
         <v>385</v>
       </c>
-      <c r="I240" s="83" t="s">
-        <v>734</v>
-      </c>
-      <c r="J240" s="82" t="s">
-        <v>735</v>
-      </c>
-      <c r="K240" s="83" t="s">
-        <v>744</v>
+      <c r="I240" s="75" t="s">
+        <v>730</v>
+      </c>
+      <c r="J240" s="74" t="s">
+        <v>731</v>
+      </c>
+      <c r="K240" s="75" t="s">
+        <v>740</v>
       </c>
       <c r="L240" s="30" t="s">
         <v>1</v>
@@ -29465,29 +29843,29 @@
       <c r="M240" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="N240" s="84" t="s">
+      <c r="N240" s="76" t="s">
         <v>386</v>
       </c>
-      <c r="O240" s="83" t="s">
-        <v>745</v>
-      </c>
-      <c r="P240" s="85" t="str">
+      <c r="O240" s="75" t="s">
+        <v>741</v>
+      </c>
+      <c r="P240" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q240" s="86" t="s">
-        <v>746</v>
-      </c>
-      <c r="R240" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="S240" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="T240" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="U240" s="87" t="s">
+      <c r="Q240" s="78" t="s">
+        <v>742</v>
+      </c>
+      <c r="R240" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S240" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="T240" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="U240" s="79" t="s">
         <v>1</v>
       </c>
       <c r="V240" s="37" t="s">
@@ -29521,15 +29899,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="22">
         <v>241</v>
       </c>
-      <c r="B241" s="81" t="s">
-        <v>747</v>
-      </c>
-      <c r="C241" s="88" t="s">
-        <v>729</v>
+      <c r="B241" s="73" t="s">
+        <v>743</v>
+      </c>
+      <c r="C241" s="80" t="s">
+        <v>763</v>
       </c>
       <c r="D241" s="37" t="s">
         <v>1</v>
@@ -29543,17 +29921,17 @@
       <c r="G241" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H241" s="82" t="s">
+      <c r="H241" s="74" t="s">
         <v>385</v>
       </c>
-      <c r="I241" s="83" t="s">
-        <v>734</v>
-      </c>
-      <c r="J241" s="82" t="s">
-        <v>735</v>
-      </c>
-      <c r="K241" s="83" t="s">
-        <v>748</v>
+      <c r="I241" s="75" t="s">
+        <v>730</v>
+      </c>
+      <c r="J241" s="74" t="s">
+        <v>731</v>
+      </c>
+      <c r="K241" s="75" t="s">
+        <v>744</v>
       </c>
       <c r="L241" s="30" t="s">
         <v>1</v>
@@ -29561,29 +29939,29 @@
       <c r="M241" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="N241" s="84" t="s">
+      <c r="N241" s="76" t="s">
         <v>386</v>
       </c>
-      <c r="O241" s="83" t="s">
-        <v>749</v>
-      </c>
-      <c r="P241" s="85" t="str">
+      <c r="O241" s="75" t="s">
+        <v>745</v>
+      </c>
+      <c r="P241" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q241" s="86" t="s">
-        <v>750</v>
-      </c>
-      <c r="R241" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="S241" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="T241" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="U241" s="87" t="s">
+      <c r="Q241" s="78" t="s">
+        <v>746</v>
+      </c>
+      <c r="R241" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S241" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="T241" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="U241" s="79" t="s">
         <v>1</v>
       </c>
       <c r="V241" s="37" t="s">
@@ -29617,15 +29995,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:31" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="89">
+    <row r="242" spans="1:31" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="81">
         <v>242</v>
       </c>
-      <c r="B242" s="81" t="s">
-        <v>751</v>
-      </c>
-      <c r="C242" s="88" t="s">
-        <v>729</v>
+      <c r="B242" s="73" t="s">
+        <v>747</v>
+      </c>
+      <c r="C242" s="80" t="s">
+        <v>763</v>
       </c>
       <c r="D242" s="37" t="s">
         <v>1</v>
@@ -29639,17 +30017,17 @@
       <c r="G242" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H242" s="82" t="s">
+      <c r="H242" s="74" t="s">
         <v>385</v>
       </c>
-      <c r="I242" s="83" t="s">
-        <v>734</v>
-      </c>
-      <c r="J242" s="82" t="s">
-        <v>735</v>
-      </c>
-      <c r="K242" s="83" t="s">
-        <v>752</v>
+      <c r="I242" s="75" t="s">
+        <v>730</v>
+      </c>
+      <c r="J242" s="74" t="s">
+        <v>731</v>
+      </c>
+      <c r="K242" s="75" t="s">
+        <v>748</v>
       </c>
       <c r="L242" s="30" t="s">
         <v>1</v>
@@ -29657,29 +30035,29 @@
       <c r="M242" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="N242" s="84" t="s">
+      <c r="N242" s="76" t="s">
         <v>386</v>
       </c>
-      <c r="O242" s="83" t="s">
-        <v>753</v>
-      </c>
-      <c r="P242" s="85" t="str">
+      <c r="O242" s="75" t="s">
+        <v>749</v>
+      </c>
+      <c r="P242" s="77" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q242" s="86" t="s">
-        <v>754</v>
-      </c>
-      <c r="R242" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="S242" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="T242" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="U242" s="87" t="s">
+      <c r="Q242" s="78" t="s">
+        <v>750</v>
+      </c>
+      <c r="R242" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S242" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="T242" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="U242" s="79" t="s">
         <v>1</v>
       </c>
       <c r="V242" s="37" t="s">
@@ -29715,41 +30093,41 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B238:B242">
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R238:U242">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:AE1">
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
